--- a/Table/car_survivor_tables.xlsx
+++ b/Table/car_survivor_tables.xlsx
@@ -1465,14 +1465,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="39" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
@@ -1480,6 +1480,11 @@
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1500,7 +1505,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>base_damage</t>
+          <t>damage</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1541,6 +1546,31 @@
       <c r="L1" s="1" t="inlineStr">
         <is>
           <t>icon_key</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>etc_value1</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>etc_value2</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>etc_value3</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>etc_value4</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>etc_value5</t>
         </is>
       </c>
     </row>
@@ -1595,6 +1625,21 @@
           <t>ico_machinegun</t>
         </is>
       </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1613,11 +1658,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>기름 장판 설치 (감속)</t>
+          <t>독 웅덩이 (지속뎀+감속)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1647,6 +1692,21 @@
           <t>ico_oilslick</t>
         </is>
       </c>
+      <c r="M3" t="n">
+        <v>50</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1665,7 +1725,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1698,6 +1758,21 @@
         <is>
           <t>ico_sawblade</t>
         </is>
+      </c>
+      <c r="M4" t="n">
+        <v>180</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5"/>
@@ -1772,7 +1847,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>base_damage</t>
+          <t>damage</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1782,7 +1857,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>기본 데미지 (레벨당 증가 기준)</t>
+          <t>기본 데미지 (레벨 스케일링 기준)</t>
         </is>
       </c>
     </row>
@@ -1919,6 +1994,91 @@
       <c r="C18" t="inlineStr">
         <is>
           <t>아이콘 리소스 키</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>etc_value1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>무기별 추가값1 (주석 참조)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>etc_value2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>무기별 추가값2 (주석 참조)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>etc_value3</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>무기별 추가값3 (주석 참조)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>etc_value4</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>무기별 추가값4 (예비)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>etc_value5</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>무기별 추가값5 (예비)</t>
         </is>
       </c>
     </row>

--- a/Table/car_survivor_tables.xlsx
+++ b/Table/car_survivor_tables.xlsx
@@ -20,6 +20,7 @@
     <sheet name="TB_LangLevelUpSelect_des" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="TB_Stage" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="Sheet1" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="TB_WarningWave" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1319,7 +1320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <sheetData>
     <row r="1">
@@ -1368,6 +1369,11 @@
           <t>arena_radius</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ww_group_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1407,7 +1413,12 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>20</v>
+        <v>50</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>WW_CH1_1</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -1448,7 +1459,12 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>20</v>
+        <v>50</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>WW_CH1_2</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -1489,7 +1505,12 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>20</v>
+        <v>50</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>WW_CH1_3</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1508,6 +1529,522 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ww_group_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>wave_no</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>mon_id</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>spawn_count</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>spawn_interval</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>max_enemies</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>difficulty_scale</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>start_time</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>WW_CH1_1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MON_001</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>초반 웨이브</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>WW_CH1_1</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>MON_002</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>60</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10초 후 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>WW_CH1_1</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>MON_003</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>80</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>20</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20초 후 강화</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>WW_CH1_1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>MON_001</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>80</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30초 후 가속</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>WW_CH1_1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>MON_004</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>45</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>45초 후 폭풍</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>WW_CH1_2</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MON_002</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>60</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Stage2 초반</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>WW_CH1_2</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MON_003</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>70</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10초 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>WW_CH1_2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MON_004</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>90</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>20</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20초 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>WW_CH1_2</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MON_001</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>100</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>35</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>35초 후 폭풍</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>WW_CH1_3</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MON_003</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>70</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Stage3 초반</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>WW_CH1_3</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>MON_004</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F12" t="n">
+        <v>80</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>10</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10초 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>WW_CH1_3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>MON_001</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>8</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F13" t="n">
+        <v>90</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" t="n">
+        <v>20</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20초 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>WW_CH1_3</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MON_002</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F14" t="n">
+        <v>100</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>30</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30초 후 최종</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 

--- a/Table/car_survivor_tables.xlsx
+++ b/Table/car_survivor_tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PBL\CarSurvival_Plan\Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D88BAB04-B53B-45D2-AB4D-A5F62EC12500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2605DBFD-312F-4ADC-88E2-8157DF8A369D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TB_Currency" sheetId="1" r:id="rId1"/>
@@ -345,7 +345,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="455">
   <si>
     <t>currency_id</t>
   </si>
@@ -1220,118 +1220,61 @@
     <t>WG_CH1</t>
   </si>
   <si>
-    <t>[00:00~00:20]</t>
-  </si>
-  <si>
     <t>시작</t>
   </si>
   <si>
-    <t>[00:20~00:40]</t>
-  </si>
-  <si>
-    <t>[00:40~01:00] MON_002 첫 등장</t>
-  </si>
-  <si>
-    <t>[01:00~01:20]</t>
-  </si>
-  <si>
     <t>스파이크 첫 등장</t>
   </si>
   <si>
-    <t>[01:20~01:40] MON_003 첫 등장</t>
-  </si>
-  <si>
-    <t>[01:40~02:00] MON_002 러시</t>
-  </si>
-  <si>
     <t>첫 혼합</t>
   </si>
   <si>
-    <t>[02:00~02:30]</t>
-  </si>
-  <si>
     <t>MON_002 러시</t>
   </si>
   <si>
-    <t>[02:30~03:00]</t>
-  </si>
-  <si>
     <t>장갑 픽업 첫 등장</t>
   </si>
   <si>
     <t>MON_001 대량</t>
   </si>
   <si>
-    <t>[03:00~03:30]</t>
-  </si>
-  <si>
     <t>바이크+탱커</t>
   </si>
   <si>
-    <t>[03:30~04:00]</t>
-  </si>
-  <si>
     <t>탱커 러시</t>
   </si>
   <si>
     <t>3종 혼합</t>
   </si>
   <si>
-    <t>[04:00~04:40]</t>
-  </si>
-  <si>
-    <t>[04:40~05:20]</t>
-  </si>
-  <si>
     <t>불꽃 버기 첫 등장</t>
   </si>
   <si>
     <t>바이크+화염</t>
   </si>
   <si>
-    <t>[05:20~06:00]</t>
-  </si>
-  <si>
     <t>탱커+화염</t>
   </si>
   <si>
-    <t>[06:00~06:40]</t>
-  </si>
-  <si>
     <t>MON_001 대러시</t>
   </si>
   <si>
-    <t>[06:40~07:20] MON_003 재등장</t>
-  </si>
-  <si>
     <t>화염 러시</t>
   </si>
   <si>
     <t>고속+화염</t>
   </si>
   <si>
-    <t>[07:20~08:00]</t>
-  </si>
-  <si>
     <t>탱커 대량</t>
   </si>
   <si>
     <t>전종 혼합</t>
   </si>
   <si>
-    <t>[08:00~08:40]</t>
-  </si>
-  <si>
-    <t>[08:40~09:20]</t>
-  </si>
-  <si>
     <t>화염 대러시</t>
   </si>
   <si>
     <t>최고속 러시</t>
-  </si>
-  <si>
-    <t>[09:20~10:00] 최종</t>
   </si>
   <si>
     <t>level</t>
@@ -1616,13 +1559,181 @@
   <si>
     <t>bounce_speed</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MON_005</t>
+  </si>
+  <si>
+    <t>MON_005</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MON_006</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MON_007</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MON_008</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MON_009</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MON_010</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MON_011</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>[00:00~00:30] 시작 / 타이어 좀비만</t>
+  </si>
+  <si>
+    <t>[00:30~01:00] Cone Head 첫 등장</t>
+  </si>
+  <si>
+    <t>★ Cone Head 첫 등장</t>
+  </si>
+  <si>
+    <t>[01:00~01:20] Oil Slime 첫 등장</t>
+  </si>
+  <si>
+    <t>★ Oil Slime 첫 등장</t>
+  </si>
+  <si>
+    <t>[01:20~01:40] 3종 혼합</t>
+  </si>
+  <si>
+    <t>[01:40~02:00] Spark Runner 첫 등장</t>
+  </si>
+  <si>
+    <t>★ Spark Runner 첫 등장 (FlameTrail)</t>
+  </si>
+  <si>
+    <t>[02:00~02:30] 고속 콤보</t>
+  </si>
+  <si>
+    <t>[02:30~03:00] Metal Crusher 첫 등장</t>
+  </si>
+  <si>
+    <t>★ Metal Crusher 첫 등장 (탱커)</t>
+  </si>
+  <si>
+    <t>[03:00~03:30] 탱커+고속 압박</t>
+  </si>
+  <si>
+    <t>[03:30~04:00] 4종 혼합</t>
+  </si>
+  <si>
+    <t>[04:00~04:30] Stoplight Striker 첫 등장</t>
+  </si>
+  <si>
+    <t>★ Stoplight Striker 첫 등장</t>
+  </si>
+  <si>
+    <t>[04:30~05:00] 고속+중형 콤보</t>
+  </si>
+  <si>
+    <t>[05:00~05:30] Wrecker Crawler 첫 등장</t>
+  </si>
+  <si>
+    <t>★ Wrecker Crawler 첫 등장</t>
+  </si>
+  <si>
+    <t>[05:30~06:00] 5종 혼합</t>
+  </si>
+  <si>
+    <t>[06:00~06:30] Billboard Golem 첫 등장</t>
+  </si>
+  <si>
+    <t>★ Billboard Golem 첫 등장 (초탱커)</t>
+  </si>
+  <si>
+    <t>[06:30~07:00] 탱커 러시</t>
+  </si>
+  <si>
+    <t>[07:00~07:30] Wrench Goblin 첫 등장</t>
+  </si>
+  <si>
+    <t>★ Wrench Goblin 첫 등장 (HP 500)</t>
+  </si>
+  <si>
+    <t>[07:30~08:00] 고난이도 전종 혼합</t>
+  </si>
+  <si>
+    <t>[08:00~08:30] 스피드+중장갑 혼합</t>
+  </si>
+  <si>
+    <t>[08:30~09:00] 탱커 대량 등장</t>
+  </si>
+  <si>
+    <t>[09:00~10:00] 최종 — 전종 혼합</t>
+  </si>
+  <si>
+    <t>[10:00~11:00] 🟢 쉬움 강화 — EXP↑ / 골드↑</t>
+  </si>
+  <si>
+    <t>보상: 경험치↑ / 골드↑</t>
+  </si>
+  <si>
+    <t>[11:00~12:00] 🟡 보통 강화 — EXP↑↑ / 보물상자 등장</t>
+  </si>
+  <si>
+    <t>보상: 경험치↑↑ / 보물상자 등장</t>
+  </si>
+  <si>
+    <t>[12:00~13:00] 🔴 어려움 강화 — EXP↑↑↑ / 보물상자↑ / 골드↑↑</t>
+  </si>
+  <si>
+    <t>보상: 경험치↑↑↑ / 보물상자↑ / 골드↑↑</t>
+  </si>
+  <si>
+    <t>[13:00~] ☠️ 감당 불가 — 사실상 즉사 구간</t>
+  </si>
+  <si>
+    <t>보상 없음 — 여기서 버티다 죽으면 게임오버</t>
+  </si>
+  <si>
+    <t>MON_027</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MON_028</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MON_029</t>
+  </si>
+  <si>
+    <t>MON_030</t>
+  </si>
+  <si>
+    <t>MON_031</t>
+  </si>
+  <si>
+    <t>MON_032</t>
+  </si>
+  <si>
+    <t>MON_033</t>
+  </si>
+  <si>
+    <t>MON_034</t>
+  </si>
+  <si>
+    <t>MON_035</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1652,8 +1763,19 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1672,8 +1794,32 @@
         <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1681,14 +1827,47 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBBBBBB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBBBBBB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBBBBBB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBBBBBB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2120,13 +2299,13 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>342</v>
+        <v>323</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>343</v>
+        <v>324</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>344</v>
+        <v>325</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>163</v>
@@ -2135,13 +2314,13 @@
         <v>283</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>345</v>
+        <v>326</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>346</v>
+        <v>327</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>34</v>
@@ -2149,13 +2328,13 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="B2" t="s">
-        <v>349</v>
+        <v>330</v>
       </c>
       <c r="C2" t="s">
-        <v>350</v>
+        <v>331</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -2164,7 +2343,7 @@
         <v>290</v>
       </c>
       <c r="F2" t="s">
-        <v>351</v>
+        <v>332</v>
       </c>
       <c r="G2">
         <v>4</v>
@@ -2189,35 +2368,35 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>342</v>
+        <v>323</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>352</v>
+        <v>333</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>343</v>
+        <v>324</v>
       </c>
       <c r="B6" t="s">
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>353</v>
+        <v>334</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>344</v>
+        <v>325</v>
       </c>
       <c r="B7" t="s">
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>354</v>
+        <v>335</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
@@ -2228,7 +2407,7 @@
         <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>355</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
@@ -2239,40 +2418,40 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>356</v>
+        <v>337</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>345</v>
+        <v>326</v>
       </c>
       <c r="B10" t="s">
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>357</v>
+        <v>338</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>346</v>
+        <v>327</v>
       </c>
       <c r="B11" t="s">
         <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>358</v>
+        <v>339</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>359</v>
+        <v>340</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.45">
@@ -2299,13 +2478,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="B1" t="s">
-        <v>361</v>
+        <v>342</v>
       </c>
       <c r="C1" t="s">
-        <v>362</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
@@ -2313,10 +2492,10 @@
         <v>89</v>
       </c>
       <c r="B2" t="s">
-        <v>363</v>
+        <v>344</v>
       </c>
       <c r="C2" t="s">
-        <v>364</v>
+        <v>345</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
@@ -2324,10 +2503,10 @@
         <v>96</v>
       </c>
       <c r="B3" t="s">
-        <v>365</v>
+        <v>346</v>
       </c>
       <c r="C3" t="s">
-        <v>366</v>
+        <v>347</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
@@ -2335,10 +2514,10 @@
         <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>367</v>
+        <v>348</v>
       </c>
       <c r="C4" t="s">
-        <v>368</v>
+        <v>349</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
@@ -2346,10 +2525,10 @@
         <v>130</v>
       </c>
       <c r="B5" t="s">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="C5" t="s">
-        <v>370</v>
+        <v>351</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
@@ -2357,10 +2536,10 @@
         <v>134</v>
       </c>
       <c r="B6" t="s">
-        <v>371</v>
+        <v>352</v>
       </c>
       <c r="C6" t="s">
-        <v>372</v>
+        <v>353</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.45">
@@ -2368,10 +2547,10 @@
         <v>139</v>
       </c>
       <c r="B7" t="s">
-        <v>373</v>
+        <v>354</v>
       </c>
       <c r="C7" t="s">
-        <v>374</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -2387,13 +2566,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="B1" t="s">
-        <v>361</v>
+        <v>342</v>
       </c>
       <c r="C1" t="s">
-        <v>362</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
@@ -2401,10 +2580,10 @@
         <v>89</v>
       </c>
       <c r="B2" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="C2" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
@@ -2412,10 +2591,10 @@
         <v>96</v>
       </c>
       <c r="B3" t="s">
-        <v>376</v>
+        <v>357</v>
       </c>
       <c r="C3" t="s">
-        <v>377</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
@@ -2423,10 +2602,10 @@
         <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>378</v>
+        <v>359</v>
       </c>
       <c r="C4" t="s">
-        <v>379</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
@@ -2434,10 +2613,10 @@
         <v>130</v>
       </c>
       <c r="B5" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="C5" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
@@ -2445,10 +2624,10 @@
         <v>134</v>
       </c>
       <c r="B6" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="C6" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.45">
@@ -2456,10 +2635,10 @@
         <v>139</v>
       </c>
       <c r="B7" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="C7" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
     </row>
   </sheetData>
@@ -2475,42 +2654,42 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>383</v>
+        <v>364</v>
       </c>
       <c r="B1" t="s">
-        <v>342</v>
+        <v>323</v>
       </c>
       <c r="C1" t="s">
-        <v>384</v>
+        <v>365</v>
       </c>
       <c r="D1" t="s">
-        <v>385</v>
+        <v>366</v>
       </c>
       <c r="E1" t="s">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="F1" t="s">
-        <v>387</v>
+        <v>368</v>
       </c>
       <c r="G1" t="s">
-        <v>388</v>
+        <v>369</v>
       </c>
       <c r="H1" t="s">
-        <v>389</v>
+        <v>370</v>
       </c>
       <c r="I1" t="s">
-        <v>390</v>
+        <v>371</v>
       </c>
       <c r="J1" t="s">
-        <v>391</v>
+        <v>372</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>392</v>
+        <v>373</v>
       </c>
       <c r="B2" t="s">
-        <v>393</v>
+        <v>374</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -2519,30 +2698,30 @@
         <v>182</v>
       </c>
       <c r="E2" t="s">
-        <v>394</v>
+        <v>375</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>395</v>
+        <v>376</v>
       </c>
       <c r="H2" t="s">
-        <v>396</v>
+        <v>377</v>
       </c>
       <c r="I2">
         <v>50</v>
       </c>
       <c r="J2" t="s">
-        <v>397</v>
+        <v>378</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>398</v>
+        <v>379</v>
       </c>
       <c r="B3" t="s">
-        <v>393</v>
+        <v>374</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -2551,30 +2730,30 @@
         <v>182</v>
       </c>
       <c r="E3" t="s">
-        <v>399</v>
+        <v>380</v>
       </c>
       <c r="F3">
         <v>5</v>
       </c>
       <c r="G3" t="s">
-        <v>400</v>
+        <v>381</v>
       </c>
       <c r="H3" t="s">
-        <v>401</v>
+        <v>382</v>
       </c>
       <c r="I3">
         <v>50</v>
       </c>
       <c r="J3" t="s">
-        <v>402</v>
+        <v>383</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>403</v>
+        <v>384</v>
       </c>
       <c r="B4" t="s">
-        <v>393</v>
+        <v>374</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -2583,22 +2762,22 @@
         <v>182</v>
       </c>
       <c r="E4" t="s">
-        <v>404</v>
+        <v>385</v>
       </c>
       <c r="F4">
         <v>8</v>
       </c>
       <c r="G4" t="s">
-        <v>405</v>
+        <v>386</v>
       </c>
       <c r="H4" t="s">
-        <v>406</v>
+        <v>387</v>
       </c>
       <c r="I4">
         <v>50</v>
       </c>
       <c r="J4" t="s">
-        <v>407</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -2625,7 +2804,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>391</v>
+        <v>372</v>
       </c>
       <c r="B1" t="s">
         <v>284</v>
@@ -2646,7 +2825,7 @@
         <v>288</v>
       </c>
       <c r="H1" t="s">
-        <v>408</v>
+        <v>389</v>
       </c>
       <c r="I1" t="s">
         <v>289</v>
@@ -2654,7 +2833,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>397</v>
+        <v>378</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -2678,12 +2857,12 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>409</v>
+        <v>390</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>397</v>
+        <v>378</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -2707,12 +2886,12 @@
         <v>10</v>
       </c>
       <c r="I3" t="s">
-        <v>410</v>
+        <v>391</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>397</v>
+        <v>378</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -2736,12 +2915,12 @@
         <v>20</v>
       </c>
       <c r="I4" t="s">
-        <v>411</v>
+        <v>392</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>397</v>
+        <v>378</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -2765,12 +2944,12 @@
         <v>30</v>
       </c>
       <c r="I5" t="s">
-        <v>412</v>
+        <v>393</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>397</v>
+        <v>378</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -2794,12 +2973,12 @@
         <v>45</v>
       </c>
       <c r="I6" t="s">
-        <v>413</v>
+        <v>394</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>402</v>
+        <v>383</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -2823,12 +3002,12 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>414</v>
+        <v>395</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>402</v>
+        <v>383</v>
       </c>
       <c r="B8">
         <v>2</v>
@@ -2852,12 +3031,12 @@
         <v>10</v>
       </c>
       <c r="I8" t="s">
-        <v>415</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>402</v>
+        <v>383</v>
       </c>
       <c r="B9">
         <v>3</v>
@@ -2881,12 +3060,12 @@
         <v>20</v>
       </c>
       <c r="I9" t="s">
-        <v>416</v>
+        <v>397</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>402</v>
+        <v>383</v>
       </c>
       <c r="B10">
         <v>4</v>
@@ -2910,12 +3089,12 @@
         <v>35</v>
       </c>
       <c r="I10" t="s">
-        <v>417</v>
+        <v>398</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>407</v>
+        <v>388</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -2939,12 +3118,12 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>418</v>
+        <v>399</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>407</v>
+        <v>388</v>
       </c>
       <c r="B12">
         <v>2</v>
@@ -2968,12 +3147,12 @@
         <v>10</v>
       </c>
       <c r="I12" t="s">
-        <v>415</v>
+        <v>396</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>407</v>
+        <v>388</v>
       </c>
       <c r="B13">
         <v>3</v>
@@ -2997,12 +3176,12 @@
         <v>20</v>
       </c>
       <c r="I13" t="s">
-        <v>416</v>
+        <v>397</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>407</v>
+        <v>388</v>
       </c>
       <c r="B14">
         <v>4</v>
@@ -3026,7 +3205,7 @@
         <v>30</v>
       </c>
       <c r="I14" t="s">
-        <v>419</v>
+        <v>400</v>
       </c>
     </row>
   </sheetData>
@@ -3118,7 +3297,7 @@
         <v>100</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F2">
         <v>1.5</v>
@@ -3868,7 +4047,8 @@
   <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="2" width="15" customWidth="1"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="22.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
@@ -4242,7 +4422,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -4255,6 +4435,8 @@
     <col min="8" max="8" width="11" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
     <col min="10" max="11" width="19" customWidth="1"/>
+    <col min="12" max="12" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.45">
@@ -4292,7 +4474,7 @@
         <v>35</v>
       </c>
       <c r="L1" t="s">
-        <v>420</v>
+        <v>401</v>
       </c>
       <c r="M1" t="s">
         <v>166</v>
@@ -4305,7 +4487,7 @@
       <c r="A2" t="s">
         <v>168</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>169</v>
       </c>
       <c r="C2" t="b">
@@ -4349,7 +4531,7 @@
       <c r="A3" t="s">
         <v>172</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>173</v>
       </c>
       <c r="C3" t="b">
@@ -4393,7 +4575,7 @@
       <c r="A4" t="s">
         <v>175</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>176</v>
       </c>
       <c r="C4" t="b">
@@ -4437,7 +4619,7 @@
       <c r="A5" t="s">
         <v>178</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="4" t="s">
         <v>179</v>
       </c>
       <c r="C5" t="b">
@@ -4479,69 +4661,66 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>182</v>
-      </c>
-      <c r="B6" t="s">
-        <v>183</v>
+        <v>403</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>193</v>
       </c>
       <c r="C6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>2000</v>
+        <v>300</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G6">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6" t="s">
-        <v>184</v>
+        <v>10</v>
       </c>
       <c r="K6" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M6">
-        <v>0.01</v>
+        <v>0.25</v>
       </c>
       <c r="N6">
-        <v>0.03</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>186</v>
-      </c>
-      <c r="B7" t="s">
-        <v>187</v>
+        <v>404</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>208</v>
       </c>
       <c r="C7" t="b">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E7">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G7">
-        <v>0.7</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -4550,7 +4729,7 @@
         <v>10</v>
       </c>
       <c r="K7" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="L7">
         <v>0.5</v>
@@ -4564,22 +4743,22 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>189</v>
-      </c>
-      <c r="B8" t="s">
-        <v>190</v>
+        <v>405</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>238</v>
       </c>
       <c r="C8" t="b">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="E8">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G8">
         <v>0.7</v>
@@ -4591,7 +4770,7 @@
         <v>10</v>
       </c>
       <c r="K8" t="s">
-        <v>191</v>
+        <v>239</v>
       </c>
       <c r="L8">
         <v>0.5</v>
@@ -4605,22 +4784,22 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>192</v>
-      </c>
-      <c r="B9" t="s">
-        <v>193</v>
+        <v>406</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>247</v>
       </c>
       <c r="C9" t="b">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="E9">
         <v>1.5</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G9">
         <v>0.7</v>
@@ -4632,7 +4811,7 @@
         <v>10</v>
       </c>
       <c r="K9" t="s">
-        <v>194</v>
+        <v>248</v>
       </c>
       <c r="L9">
         <v>0.5</v>
@@ -4646,25 +4825,25 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>195</v>
-      </c>
-      <c r="B10" t="s">
-        <v>196</v>
+        <v>407</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>250</v>
       </c>
       <c r="C10" t="b">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="E10">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G10">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -4673,13 +4852,13 @@
         <v>10</v>
       </c>
       <c r="K10" t="s">
-        <v>197</v>
+        <v>251</v>
       </c>
       <c r="L10">
         <v>0.5</v>
       </c>
       <c r="M10">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="N10">
         <v>0.15</v>
@@ -4687,51 +4866,54 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>198</v>
-      </c>
-      <c r="B11" t="s">
-        <v>199</v>
+        <v>182</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>183</v>
       </c>
       <c r="C11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11">
+        <v>2000</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
         <v>30</v>
       </c>
-      <c r="E11">
-        <v>1.5</v>
-      </c>
-      <c r="F11">
-        <v>5</v>
-      </c>
       <c r="G11">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="H11">
         <v>1</v>
       </c>
       <c r="I11">
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="J11" t="s">
+        <v>184</v>
       </c>
       <c r="K11" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="L11">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M11">
-        <v>0.25</v>
+        <v>0.01</v>
       </c>
       <c r="N11">
-        <v>0.15</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>201</v>
-      </c>
-      <c r="B12" t="s">
-        <v>202</v>
+        <v>408</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>187</v>
       </c>
       <c r="C12" t="b">
         <v>0</v>
@@ -4740,7 +4922,7 @@
         <v>30</v>
       </c>
       <c r="E12">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -4755,7 +4937,7 @@
         <v>10</v>
       </c>
       <c r="K12" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="L12">
         <v>0.5</v>
@@ -4769,10 +4951,10 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>204</v>
-      </c>
-      <c r="B13" t="s">
-        <v>205</v>
+        <v>409</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>190</v>
       </c>
       <c r="C13" t="b">
         <v>0</v>
@@ -4796,7 +4978,7 @@
         <v>10</v>
       </c>
       <c r="K13" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="L13">
         <v>0.5</v>
@@ -4810,10 +4992,10 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>207</v>
-      </c>
-      <c r="B14" t="s">
-        <v>208</v>
+        <v>204</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>196</v>
       </c>
       <c r="C14" t="b">
         <v>0</v>
@@ -4837,7 +5019,7 @@
         <v>10</v>
       </c>
       <c r="K14" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="L14">
         <v>0.5</v>
@@ -4851,10 +5033,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>210</v>
-      </c>
-      <c r="B15" t="s">
-        <v>211</v>
+        <v>207</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>199</v>
       </c>
       <c r="C15" t="b">
         <v>0</v>
@@ -4878,7 +5060,7 @@
         <v>10</v>
       </c>
       <c r="K15" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="L15">
         <v>0.5</v>
@@ -4892,10 +5074,10 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>213</v>
-      </c>
-      <c r="B16" t="s">
-        <v>214</v>
+        <v>210</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="C16" t="b">
         <v>0</v>
@@ -4919,7 +5101,7 @@
         <v>10</v>
       </c>
       <c r="K16" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="L16">
         <v>0.5</v>
@@ -4933,10 +5115,10 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>216</v>
-      </c>
-      <c r="B17" t="s">
-        <v>217</v>
+        <v>213</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>205</v>
       </c>
       <c r="C17" t="b">
         <v>0</v>
@@ -4960,7 +5142,7 @@
         <v>10</v>
       </c>
       <c r="K17" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="L17">
         <v>0.5</v>
@@ -4974,10 +5156,10 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>219</v>
-      </c>
-      <c r="B18" t="s">
-        <v>220</v>
+        <v>216</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>229</v>
       </c>
       <c r="C18" t="b">
         <v>0</v>
@@ -5001,7 +5183,7 @@
         <v>10</v>
       </c>
       <c r="K18" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="L18">
         <v>0.5</v>
@@ -5015,10 +5197,10 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>222</v>
-      </c>
-      <c r="B19" t="s">
-        <v>223</v>
+        <v>219</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>235</v>
       </c>
       <c r="C19" t="b">
         <v>0</v>
@@ -5042,7 +5224,7 @@
         <v>10</v>
       </c>
       <c r="K19" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="L19">
         <v>0.5</v>
@@ -5056,10 +5238,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>225</v>
-      </c>
-      <c r="B20" t="s">
-        <v>226</v>
+        <v>222</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>241</v>
       </c>
       <c r="C20" t="b">
         <v>0</v>
@@ -5083,7 +5265,7 @@
         <v>10</v>
       </c>
       <c r="K20" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="L20">
         <v>0.5</v>
@@ -5097,10 +5279,10 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>228</v>
-      </c>
-      <c r="B21" t="s">
-        <v>229</v>
+        <v>225</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>220</v>
       </c>
       <c r="C21" t="b">
         <v>0</v>
@@ -5124,7 +5306,7 @@
         <v>10</v>
       </c>
       <c r="K21" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="L21">
         <v>0.5</v>
@@ -5138,10 +5320,10 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>231</v>
-      </c>
-      <c r="B22" t="s">
-        <v>232</v>
+        <v>228</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>223</v>
       </c>
       <c r="C22" t="b">
         <v>0</v>
@@ -5165,7 +5347,7 @@
         <v>10</v>
       </c>
       <c r="K22" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="L22">
         <v>0.5</v>
@@ -5179,10 +5361,10 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>234</v>
-      </c>
-      <c r="B23" t="s">
-        <v>235</v>
+        <v>231</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>226</v>
       </c>
       <c r="C23" t="b">
         <v>0</v>
@@ -5206,7 +5388,7 @@
         <v>10</v>
       </c>
       <c r="K23" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="L23">
         <v>0.5</v>
@@ -5220,10 +5402,10 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>237</v>
-      </c>
-      <c r="B24" t="s">
-        <v>238</v>
+        <v>234</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>232</v>
       </c>
       <c r="C24" t="b">
         <v>0</v>
@@ -5247,7 +5429,7 @@
         <v>10</v>
       </c>
       <c r="K24" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="L24">
         <v>0.5</v>
@@ -5261,10 +5443,10 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>240</v>
-      </c>
-      <c r="B25" t="s">
-        <v>241</v>
+        <v>237</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>244</v>
       </c>
       <c r="C25" t="b">
         <v>0</v>
@@ -5288,7 +5470,7 @@
         <v>10</v>
       </c>
       <c r="K25" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="L25">
         <v>0.5</v>
@@ -5302,10 +5484,10 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>243</v>
-      </c>
-      <c r="B26" t="s">
-        <v>244</v>
+        <v>240</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>211</v>
       </c>
       <c r="C26" t="b">
         <v>0</v>
@@ -5329,7 +5511,7 @@
         <v>10</v>
       </c>
       <c r="K26" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="L26">
         <v>0.5</v>
@@ -5343,10 +5525,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>246</v>
-      </c>
-      <c r="B27" t="s">
-        <v>247</v>
+        <v>243</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>214</v>
       </c>
       <c r="C27" t="b">
         <v>0</v>
@@ -5370,7 +5552,7 @@
         <v>10</v>
       </c>
       <c r="K27" t="s">
-        <v>248</v>
+        <v>215</v>
       </c>
       <c r="L27">
         <v>0.5</v>
@@ -5384,10 +5566,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>249</v>
-      </c>
-      <c r="B28" t="s">
-        <v>250</v>
+        <v>246</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>217</v>
       </c>
       <c r="C28" t="b">
         <v>0</v>
@@ -5411,7 +5593,7 @@
         <v>10</v>
       </c>
       <c r="K28" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="L28">
         <v>0.5</v>
@@ -5420,6 +5602,387 @@
         <v>0.25</v>
       </c>
       <c r="N28">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>446</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C29" t="b">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>50</v>
+      </c>
+      <c r="E29">
+        <v>2.5</v>
+      </c>
+      <c r="F29">
+        <v>8</v>
+      </c>
+      <c r="G29">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29">
+        <v>10</v>
+      </c>
+      <c r="J29" t="s">
+        <v>170</v>
+      </c>
+      <c r="K29" t="s">
+        <v>171</v>
+      </c>
+      <c r="L29">
+        <v>0.5</v>
+      </c>
+      <c r="M29">
+        <v>0.1</v>
+      </c>
+      <c r="N29">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>447</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C30" t="b">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>30</v>
+      </c>
+      <c r="E30">
+        <v>4</v>
+      </c>
+      <c r="F30">
+        <v>6</v>
+      </c>
+      <c r="G30">
+        <v>0.5</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30">
+        <v>8</v>
+      </c>
+      <c r="J30" t="s">
+        <v>170</v>
+      </c>
+      <c r="K30" t="s">
+        <v>174</v>
+      </c>
+      <c r="L30">
+        <v>0.5</v>
+      </c>
+      <c r="M30">
+        <v>0.1</v>
+      </c>
+      <c r="N30">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>448</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C31" t="b">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>120</v>
+      </c>
+      <c r="E31">
+        <v>1.5</v>
+      </c>
+      <c r="F31">
+        <v>15</v>
+      </c>
+      <c r="G31">
+        <v>0.8</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31">
+        <v>5</v>
+      </c>
+      <c r="J31" t="s">
+        <v>170</v>
+      </c>
+      <c r="K31" t="s">
+        <v>177</v>
+      </c>
+      <c r="L31">
+        <v>0.5</v>
+      </c>
+      <c r="M31">
+        <v>0.3</v>
+      </c>
+      <c r="N31">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>449</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C32" t="b">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>40</v>
+      </c>
+      <c r="E32">
+        <v>5</v>
+      </c>
+      <c r="F32">
+        <v>10</v>
+      </c>
+      <c r="G32">
+        <v>0.6</v>
+      </c>
+      <c r="H32">
+        <v>1</v>
+      </c>
+      <c r="I32">
+        <v>6</v>
+      </c>
+      <c r="J32" t="s">
+        <v>180</v>
+      </c>
+      <c r="K32" t="s">
+        <v>181</v>
+      </c>
+      <c r="L32">
+        <v>0.5</v>
+      </c>
+      <c r="M32">
+        <v>0.1</v>
+      </c>
+      <c r="N32">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>450</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C33" t="b">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>300</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="F33">
+        <v>15</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="I33">
+        <v>10</v>
+      </c>
+      <c r="K33" t="s">
+        <v>194</v>
+      </c>
+      <c r="L33">
+        <v>0.5</v>
+      </c>
+      <c r="M33">
+        <v>0.25</v>
+      </c>
+      <c r="N33">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>451</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C34" t="b">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>50</v>
+      </c>
+      <c r="E34">
+        <v>2.5</v>
+      </c>
+      <c r="F34">
+        <v>8</v>
+      </c>
+      <c r="G34">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+      <c r="I34">
+        <v>10</v>
+      </c>
+      <c r="K34" t="s">
+        <v>209</v>
+      </c>
+      <c r="L34">
+        <v>0.5</v>
+      </c>
+      <c r="M34">
+        <v>0.25</v>
+      </c>
+      <c r="N34">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>452</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C35" t="b">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>100</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+      <c r="F35">
+        <v>10</v>
+      </c>
+      <c r="G35">
+        <v>0.7</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35">
+        <v>10</v>
+      </c>
+      <c r="K35" t="s">
+        <v>239</v>
+      </c>
+      <c r="L35">
+        <v>0.5</v>
+      </c>
+      <c r="M35">
+        <v>0.25</v>
+      </c>
+      <c r="N35">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>453</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C36" t="b">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>100</v>
+      </c>
+      <c r="E36">
+        <v>1.5</v>
+      </c>
+      <c r="F36">
+        <v>10</v>
+      </c>
+      <c r="G36">
+        <v>0.7</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36">
+        <v>10</v>
+      </c>
+      <c r="K36" t="s">
+        <v>248</v>
+      </c>
+      <c r="L36">
+        <v>0.5</v>
+      </c>
+      <c r="M36">
+        <v>0.25</v>
+      </c>
+      <c r="N36">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>454</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C37" t="b">
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <v>500</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+      <c r="F37">
+        <v>20</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="H37">
+        <v>1</v>
+      </c>
+      <c r="I37">
+        <v>10</v>
+      </c>
+      <c r="K37" t="s">
+        <v>251</v>
+      </c>
+      <c r="L37">
+        <v>0.5</v>
+      </c>
+      <c r="M37">
+        <v>0.1</v>
+      </c>
+      <c r="N37">
         <v>0.15</v>
       </c>
     </row>
@@ -5465,13 +6028,13 @@
       <c r="B2" t="s">
         <v>168</v>
       </c>
-      <c r="C2">
-        <v>8</v>
-      </c>
-      <c r="D2">
+      <c r="C2" s="6">
+        <v>2</v>
+      </c>
+      <c r="D2" s="7">
         <v>5</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="7">
         <v>0</v>
       </c>
     </row>
@@ -5482,13 +6045,13 @@
       <c r="B3" t="s">
         <v>172</v>
       </c>
-      <c r="C3">
-        <v>15</v>
-      </c>
-      <c r="D3">
+      <c r="C3" s="6">
+        <v>2</v>
+      </c>
+      <c r="D3" s="7">
         <v>3</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="7">
         <v>0</v>
       </c>
     </row>
@@ -5499,13 +6062,13 @@
       <c r="B4" t="s">
         <v>175</v>
       </c>
-      <c r="C4">
-        <v>20</v>
-      </c>
-      <c r="D4">
+      <c r="C4" s="6">
+        <v>6</v>
+      </c>
+      <c r="D4" s="7">
         <v>10</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="7">
         <v>1</v>
       </c>
     </row>
@@ -5516,13 +6079,13 @@
       <c r="B5" t="s">
         <v>178</v>
       </c>
-      <c r="C5">
-        <v>25</v>
-      </c>
-      <c r="D5">
+      <c r="C5" s="6">
+        <v>4</v>
+      </c>
+      <c r="D5" s="7">
         <v>6</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="7">
         <v>0</v>
       </c>
     </row>
@@ -5533,13 +6096,13 @@
       <c r="B6" t="s">
         <v>182</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="6">
         <v>50</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="7">
         <v>200</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="7">
         <v>20</v>
       </c>
     </row>
@@ -5550,13 +6113,13 @@
       <c r="B7" t="s">
         <v>186</v>
       </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7">
+      <c r="C7" s="6">
+        <v>2</v>
+      </c>
+      <c r="D7" s="7">
         <v>5</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="7">
         <v>0</v>
       </c>
     </row>
@@ -5567,13 +6130,13 @@
       <c r="B8" t="s">
         <v>189</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="6">
         <v>3</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="7">
         <v>5</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="7">
         <v>0</v>
       </c>
     </row>
@@ -5584,13 +6147,13 @@
       <c r="B9" t="s">
         <v>192</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="6">
         <v>3</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="7">
         <v>5</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="7">
         <v>0</v>
       </c>
     </row>
@@ -5601,13 +6164,13 @@
       <c r="B10" t="s">
         <v>195</v>
       </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-      <c r="D10">
-        <v>5</v>
-      </c>
-      <c r="E10">
+      <c r="C10" s="6">
+        <v>8</v>
+      </c>
+      <c r="D10" s="7">
+        <v>8</v>
+      </c>
+      <c r="E10" s="7">
         <v>0</v>
       </c>
     </row>
@@ -5618,13 +6181,13 @@
       <c r="B11" t="s">
         <v>198</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="8">
         <v>3</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="8">
         <v>5</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="8">
         <v>0</v>
       </c>
     </row>
@@ -5635,13 +6198,13 @@
       <c r="B12" t="s">
         <v>201</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="8">
         <v>3</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="8">
         <v>5</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="8">
         <v>0</v>
       </c>
     </row>
@@ -5652,13 +6215,13 @@
       <c r="B13" t="s">
         <v>204</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="8">
         <v>3</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="8">
         <v>5</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="8">
         <v>0</v>
       </c>
     </row>
@@ -5669,13 +6232,13 @@
       <c r="B14" t="s">
         <v>207</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="8">
         <v>3</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="8">
         <v>5</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="8">
         <v>0</v>
       </c>
     </row>
@@ -5686,13 +6249,13 @@
       <c r="B15" t="s">
         <v>210</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="8">
         <v>3</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="8">
         <v>5</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="8">
         <v>0</v>
       </c>
     </row>
@@ -5703,13 +6266,13 @@
       <c r="B16" t="s">
         <v>213</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="8">
         <v>3</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="8">
         <v>5</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="8">
         <v>0</v>
       </c>
     </row>
@@ -5720,13 +6283,13 @@
       <c r="B17" t="s">
         <v>216</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="8">
         <v>3</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="8">
         <v>5</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="8">
         <v>0</v>
       </c>
     </row>
@@ -5737,13 +6300,13 @@
       <c r="B18" t="s">
         <v>219</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="8">
         <v>3</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="8">
         <v>5</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="8">
         <v>0</v>
       </c>
     </row>
@@ -5754,13 +6317,13 @@
       <c r="B19" t="s">
         <v>222</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="8">
         <v>3</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="8">
         <v>5</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="8">
         <v>0</v>
       </c>
     </row>
@@ -5771,13 +6334,13 @@
       <c r="B20" t="s">
         <v>225</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="8">
         <v>3</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="8">
         <v>5</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="8">
         <v>0</v>
       </c>
     </row>
@@ -5788,13 +6351,13 @@
       <c r="B21" t="s">
         <v>228</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="8">
         <v>3</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="8">
         <v>5</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="8">
         <v>0</v>
       </c>
     </row>
@@ -5805,13 +6368,13 @@
       <c r="B22" t="s">
         <v>231</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="8">
         <v>3</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="8">
         <v>5</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="8">
         <v>0</v>
       </c>
     </row>
@@ -5822,13 +6385,13 @@
       <c r="B23" t="s">
         <v>234</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="8">
         <v>3</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="8">
         <v>5</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="8">
         <v>0</v>
       </c>
     </row>
@@ -5839,13 +6402,13 @@
       <c r="B24" t="s">
         <v>237</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="8">
         <v>3</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="8">
         <v>5</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="8">
         <v>0</v>
       </c>
     </row>
@@ -5856,13 +6419,13 @@
       <c r="B25" t="s">
         <v>240</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="8">
         <v>3</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="8">
         <v>5</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="8">
         <v>0</v>
       </c>
     </row>
@@ -5873,13 +6436,13 @@
       <c r="B26" t="s">
         <v>243</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="8">
         <v>3</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="8">
         <v>5</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="8">
         <v>0</v>
       </c>
     </row>
@@ -5890,13 +6453,13 @@
       <c r="B27" t="s">
         <v>246</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="8">
         <v>3</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="8">
         <v>5</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="8">
         <v>0</v>
       </c>
     </row>
@@ -5907,13 +6470,13 @@
       <c r="B28" t="s">
         <v>249</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="8">
         <v>3</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="8">
         <v>5</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="8">
         <v>0</v>
       </c>
     </row>
@@ -5926,7 +6489,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -5972,1084 +6535,2144 @@
         <v>289</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+    <row r="2" spans="1:10" ht="25" x14ac:dyDescent="0.45">
+      <c r="A2" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="10">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>6</v>
-      </c>
-      <c r="F2">
+      <c r="D2" s="10">
+        <v>3</v>
+      </c>
+      <c r="E2" s="10">
+        <v>5</v>
+      </c>
+      <c r="F2" s="10">
         <v>15</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="10">
         <v>1</v>
       </c>
-      <c r="H2" t="s">
-        <v>291</v>
+      <c r="H2" s="10" t="s">
+        <v>410</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="25" x14ac:dyDescent="0.45">
+      <c r="A3" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="10">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="10">
         <v>3</v>
       </c>
-      <c r="E3">
-        <v>6</v>
-      </c>
-      <c r="F3">
+      <c r="E3" s="10">
+        <v>5</v>
+      </c>
+      <c r="F3" s="10">
         <v>18</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="10">
         <v>1.05</v>
       </c>
-      <c r="H3" t="s">
-        <v>293</v>
+      <c r="H3" s="10" t="s">
+        <v>411</v>
       </c>
       <c r="I3">
         <v>1.05</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
+      <c r="A4" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4" t="s">
-        <v>168</v>
-      </c>
-      <c r="D4">
+      <c r="B4" s="10">
         <v>2</v>
       </c>
-      <c r="E4">
-        <v>6</v>
-      </c>
-      <c r="F4">
-        <v>20</v>
-      </c>
-      <c r="G4">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="H4" t="s">
-        <v>294</v>
+      <c r="C4" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="D4" s="10">
+        <v>2</v>
+      </c>
+      <c r="E4" s="10">
+        <v>5</v>
+      </c>
+      <c r="F4" s="10">
+        <v>18</v>
+      </c>
+      <c r="G4" s="10">
+        <v>1.05</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>412</v>
       </c>
       <c r="I4">
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
+    <row r="5" spans="1:10" ht="25" x14ac:dyDescent="0.45">
+      <c r="A5" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="10">
         <v>3</v>
       </c>
-      <c r="C5" t="s">
-        <v>172</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>6</v>
-      </c>
-      <c r="F5">
-        <v>20</v>
-      </c>
-      <c r="G5">
+      <c r="C5" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="D5" s="10">
+        <v>3</v>
+      </c>
+      <c r="E5" s="10">
+        <v>4</v>
+      </c>
+      <c r="F5" s="10">
+        <v>22</v>
+      </c>
+      <c r="G5" s="10">
         <v>1.1000000000000001</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>413</v>
       </c>
       <c r="I5">
         <v>1.1499999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
+      <c r="A6" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="10">
+        <v>3</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="D6" s="10">
+        <v>2</v>
+      </c>
+      <c r="E6" s="10">
         <v>4</v>
       </c>
-      <c r="C6" t="s">
-        <v>168</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
+      <c r="F6" s="10">
         <v>22</v>
       </c>
-      <c r="G6">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="H6" t="s">
-        <v>295</v>
+      <c r="G6" s="10">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>414</v>
       </c>
       <c r="I6">
         <v>1.2</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
+      <c r="A7" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="10">
         <v>4</v>
       </c>
-      <c r="C7" t="s">
-        <v>172</v>
-      </c>
-      <c r="D7">
+      <c r="C7" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="D7" s="10">
         <v>2</v>
       </c>
-      <c r="E7">
-        <v>6</v>
-      </c>
-      <c r="F7">
-        <v>22</v>
-      </c>
-      <c r="G7">
+      <c r="E7" s="10">
+        <v>4</v>
+      </c>
+      <c r="F7" s="10">
+        <v>25</v>
+      </c>
+      <c r="G7" s="10">
         <v>1.1499999999999999</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>415</v>
       </c>
       <c r="I7">
         <v>1.2</v>
       </c>
       <c r="J7" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
+      <c r="A8" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B8">
-        <v>5</v>
-      </c>
-      <c r="C8" t="s">
-        <v>168</v>
-      </c>
-      <c r="D8">
+      <c r="B8" s="10">
+        <v>4</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="D8" s="10">
         <v>2</v>
       </c>
-      <c r="E8">
-        <v>6</v>
-      </c>
-      <c r="F8">
+      <c r="E8" s="10">
+        <v>4</v>
+      </c>
+      <c r="F8" s="10">
         <v>25</v>
       </c>
-      <c r="G8">
-        <v>1.2</v>
-      </c>
-      <c r="H8" t="s">
-        <v>297</v>
-      </c>
+      <c r="G8" s="10">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="H8" s="10"/>
       <c r="I8">
         <v>1.25</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
+      <c r="A9" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B9">
-        <v>5</v>
-      </c>
-      <c r="C9" t="s">
-        <v>175</v>
-      </c>
-      <c r="D9">
+      <c r="B9" s="10">
+        <v>4</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="D9" s="10">
         <v>2</v>
       </c>
-      <c r="E9">
-        <v>6</v>
-      </c>
-      <c r="F9">
+      <c r="E9" s="10">
+        <v>4</v>
+      </c>
+      <c r="F9" s="10">
         <v>25</v>
       </c>
-      <c r="G9">
-        <v>1.2</v>
-      </c>
+      <c r="G9" s="10">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="H9" s="10"/>
       <c r="I9">
         <v>1.3</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
+    <row r="10" spans="1:10" ht="25" x14ac:dyDescent="0.45">
+      <c r="A10" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B10">
-        <v>6</v>
-      </c>
-      <c r="C10" t="s">
-        <v>172</v>
-      </c>
-      <c r="D10">
+      <c r="B10" s="10">
+        <v>5</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="D10" s="10">
+        <v>2</v>
+      </c>
+      <c r="E10" s="10">
         <v>4</v>
       </c>
-      <c r="E10">
-        <v>6</v>
-      </c>
-      <c r="F10">
+      <c r="F10" s="10">
         <v>28</v>
       </c>
-      <c r="G10">
-        <v>1.25</v>
-      </c>
-      <c r="H10" t="s">
-        <v>298</v>
+      <c r="G10" s="10">
+        <v>1.2</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>416</v>
       </c>
       <c r="I10">
         <v>1.3</v>
       </c>
       <c r="J10" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="25" x14ac:dyDescent="0.45">
+      <c r="A11" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B11">
-        <v>7</v>
-      </c>
-      <c r="C11" t="s">
-        <v>172</v>
-      </c>
-      <c r="D11">
-        <v>3</v>
-      </c>
-      <c r="E11">
-        <v>6</v>
-      </c>
-      <c r="F11">
-        <v>30</v>
-      </c>
-      <c r="G11">
-        <v>1.3</v>
-      </c>
-      <c r="H11" t="s">
-        <v>300</v>
+      <c r="B11" s="10">
+        <v>5</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="D11" s="10">
+        <v>2</v>
+      </c>
+      <c r="E11" s="10">
+        <v>4</v>
+      </c>
+      <c r="F11" s="10">
+        <v>28</v>
+      </c>
+      <c r="G11" s="10">
+        <v>1.2</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>417</v>
       </c>
       <c r="I11">
         <v>1.3</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
+      <c r="A12" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B12">
-        <v>7</v>
-      </c>
-      <c r="C12" t="s">
-        <v>175</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12">
+      <c r="B12" s="10">
         <v>6</v>
       </c>
-      <c r="F12">
+      <c r="C12" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="D12" s="10">
+        <v>2</v>
+      </c>
+      <c r="E12" s="10">
+        <v>4</v>
+      </c>
+      <c r="F12" s="10">
         <v>30</v>
       </c>
-      <c r="G12">
-        <v>1.3</v>
+      <c r="G12" s="10">
+        <v>1.25</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>418</v>
       </c>
       <c r="I12">
         <v>1.35</v>
       </c>
       <c r="J12" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
+      <c r="A13" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B13">
-        <v>8</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="B13" s="10">
+        <v>6</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="D13">
-        <v>2</v>
-      </c>
-      <c r="E13">
-        <v>6</v>
-      </c>
-      <c r="F13">
-        <v>32</v>
-      </c>
-      <c r="G13">
-        <v>1.4</v>
-      </c>
-      <c r="H13" t="s">
-        <v>302</v>
-      </c>
+      <c r="D13" s="10">
+        <v>3</v>
+      </c>
+      <c r="E13" s="10">
+        <v>4</v>
+      </c>
+      <c r="F13" s="10">
+        <v>30</v>
+      </c>
+      <c r="G13" s="10">
+        <v>1.25</v>
+      </c>
+      <c r="H13" s="10"/>
       <c r="I13">
         <v>1.4</v>
       </c>
       <c r="J13" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
+      <c r="A14" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B14">
-        <v>8</v>
-      </c>
-      <c r="C14" t="s">
-        <v>172</v>
-      </c>
-      <c r="D14">
+      <c r="B14" s="10">
+        <v>6</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="D14" s="10">
         <v>2</v>
       </c>
-      <c r="E14">
-        <v>6</v>
-      </c>
-      <c r="F14">
-        <v>32</v>
-      </c>
-      <c r="G14">
-        <v>1.4</v>
-      </c>
+      <c r="E14" s="10">
+        <v>4</v>
+      </c>
+      <c r="F14" s="10">
+        <v>30</v>
+      </c>
+      <c r="G14" s="10">
+        <v>1.25</v>
+      </c>
+      <c r="H14" s="10"/>
       <c r="I14">
         <v>1.45</v>
       </c>
       <c r="J14" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="25" x14ac:dyDescent="0.45">
+      <c r="A15" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B15">
-        <v>9</v>
-      </c>
-      <c r="C15" t="s">
-        <v>172</v>
-      </c>
-      <c r="D15">
+      <c r="B15" s="10">
+        <v>7</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="D15" s="10">
         <v>2</v>
       </c>
-      <c r="E15">
-        <v>6</v>
-      </c>
-      <c r="F15">
-        <v>35</v>
-      </c>
-      <c r="G15">
-        <v>1.5</v>
-      </c>
-      <c r="H15" t="s">
-        <v>305</v>
+      <c r="E15" s="10">
+        <v>4</v>
+      </c>
+      <c r="F15" s="10">
+        <v>32</v>
+      </c>
+      <c r="G15" s="10">
+        <v>1.3</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>419</v>
       </c>
       <c r="I15">
         <v>1.5</v>
       </c>
       <c r="J15" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="25" x14ac:dyDescent="0.45">
+      <c r="A16" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B16">
-        <v>9</v>
-      </c>
-      <c r="C16" t="s">
-        <v>172</v>
-      </c>
-      <c r="D16">
-        <v>2</v>
-      </c>
-      <c r="E16">
-        <v>6</v>
-      </c>
-      <c r="F16">
-        <v>35</v>
-      </c>
-      <c r="G16">
-        <v>1.5</v>
+      <c r="B16" s="10">
+        <v>7</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D16" s="10">
+        <v>1</v>
+      </c>
+      <c r="E16" s="10">
+        <v>5</v>
+      </c>
+      <c r="F16" s="10">
+        <v>32</v>
+      </c>
+      <c r="G16" s="10">
+        <v>1.3</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>420</v>
       </c>
       <c r="I16">
         <v>1.5</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
+      <c r="A17" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B17">
-        <v>10</v>
-      </c>
-      <c r="C17" t="s">
-        <v>172</v>
-      </c>
-      <c r="D17">
-        <v>3</v>
-      </c>
-      <c r="E17">
-        <v>6</v>
-      </c>
-      <c r="F17">
-        <v>38</v>
-      </c>
-      <c r="G17">
-        <v>1.6</v>
-      </c>
-      <c r="H17" t="s">
-        <v>307</v>
-      </c>
+      <c r="B17" s="10">
+        <v>7</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="D17" s="10">
+        <v>2</v>
+      </c>
+      <c r="E17" s="10">
+        <v>4</v>
+      </c>
+      <c r="F17" s="10">
+        <v>32</v>
+      </c>
+      <c r="G17" s="10">
+        <v>1.3</v>
+      </c>
+      <c r="H17" s="10"/>
       <c r="I17">
         <v>1.55</v>
       </c>
       <c r="J17" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="25" x14ac:dyDescent="0.45">
+      <c r="A18" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B18">
-        <v>10</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="B18" s="10">
+        <v>8</v>
+      </c>
+      <c r="C18" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="D18">
-        <v>2</v>
-      </c>
-      <c r="E18">
-        <v>6</v>
-      </c>
-      <c r="F18">
-        <v>38</v>
-      </c>
-      <c r="G18">
-        <v>1.6</v>
+      <c r="D18" s="10">
+        <v>3</v>
+      </c>
+      <c r="E18" s="10">
+        <v>4</v>
+      </c>
+      <c r="F18" s="10">
+        <v>35</v>
+      </c>
+      <c r="G18" s="10">
+        <v>1.35</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>421</v>
       </c>
       <c r="I18">
         <v>1.6</v>
       </c>
       <c r="J18" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
+      <c r="A19" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B19">
-        <v>11</v>
-      </c>
-      <c r="C19" t="s">
-        <v>172</v>
-      </c>
-      <c r="D19">
-        <v>3</v>
-      </c>
-      <c r="E19">
-        <v>6</v>
-      </c>
-      <c r="F19">
-        <v>40</v>
-      </c>
-      <c r="G19">
-        <v>1.7</v>
-      </c>
-      <c r="H19" t="s">
-        <v>310</v>
-      </c>
+      <c r="B19" s="10">
+        <v>8</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D19" s="10">
+        <v>2</v>
+      </c>
+      <c r="E19" s="10">
+        <v>5</v>
+      </c>
+      <c r="F19" s="10">
+        <v>35</v>
+      </c>
+      <c r="G19" s="10">
+        <v>1.35</v>
+      </c>
+      <c r="H19" s="10"/>
       <c r="I19">
         <v>1.6</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
+      <c r="A20" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B20">
-        <v>11</v>
-      </c>
-      <c r="C20" t="s">
-        <v>172</v>
-      </c>
-      <c r="D20">
-        <v>3</v>
-      </c>
-      <c r="E20">
-        <v>6</v>
-      </c>
-      <c r="F20">
-        <v>40</v>
-      </c>
-      <c r="G20">
-        <v>1.7</v>
-      </c>
+      <c r="B20" s="10">
+        <v>8</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="D20" s="10">
+        <v>2</v>
+      </c>
+      <c r="E20" s="10">
+        <v>4</v>
+      </c>
+      <c r="F20" s="10">
+        <v>35</v>
+      </c>
+      <c r="G20" s="10">
+        <v>1.35</v>
+      </c>
+      <c r="H20" s="10"/>
       <c r="I20">
         <v>1.6</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
+      <c r="A21" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B21">
-        <v>12</v>
-      </c>
-      <c r="C21" t="s">
-        <v>172</v>
-      </c>
-      <c r="D21">
+      <c r="B21" s="10">
+        <v>9</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="D21" s="10">
+        <v>2</v>
+      </c>
+      <c r="E21" s="10">
         <v>4</v>
       </c>
-      <c r="E21">
-        <v>6</v>
-      </c>
-      <c r="F21">
-        <v>42</v>
-      </c>
-      <c r="G21">
-        <v>1.8</v>
-      </c>
-      <c r="H21" t="s">
-        <v>311</v>
+      <c r="F21" s="10">
+        <v>38</v>
+      </c>
+      <c r="G21" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>422</v>
       </c>
       <c r="I21">
         <v>1.7</v>
       </c>
       <c r="J21" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
+      <c r="A22" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B22">
-        <v>12</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="B22" s="10">
+        <v>9</v>
+      </c>
+      <c r="C22" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="10">
         <v>3</v>
       </c>
-      <c r="E22">
-        <v>6</v>
-      </c>
-      <c r="F22">
-        <v>42</v>
-      </c>
-      <c r="G22">
-        <v>1.8</v>
-      </c>
+      <c r="E22" s="10">
+        <v>4</v>
+      </c>
+      <c r="F22" s="10">
+        <v>38</v>
+      </c>
+      <c r="G22" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="H22" s="10"/>
       <c r="I22">
         <v>1.8</v>
       </c>
       <c r="J22" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
+      <c r="A23" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B23">
-        <v>13</v>
-      </c>
-      <c r="C23" t="s">
-        <v>172</v>
-      </c>
-      <c r="D23">
-        <v>4</v>
-      </c>
-      <c r="E23">
-        <v>6</v>
-      </c>
-      <c r="F23">
-        <v>45</v>
-      </c>
-      <c r="G23">
-        <v>1.9</v>
-      </c>
-      <c r="H23" t="s">
-        <v>314</v>
-      </c>
+      <c r="B23" s="10">
+        <v>9</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D23" s="10">
+        <v>2</v>
+      </c>
+      <c r="E23" s="10">
+        <v>5</v>
+      </c>
+      <c r="F23" s="10">
+        <v>38</v>
+      </c>
+      <c r="G23" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="H23" s="10"/>
       <c r="I23">
         <v>1.8</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
+      <c r="A24" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B24">
-        <v>13</v>
-      </c>
-      <c r="C24" t="s">
-        <v>172</v>
-      </c>
-      <c r="D24">
-        <v>3</v>
-      </c>
-      <c r="E24">
-        <v>6</v>
-      </c>
-      <c r="F24">
-        <v>45</v>
-      </c>
-      <c r="G24">
-        <v>1.9</v>
-      </c>
+      <c r="B24" s="10">
+        <v>9</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="D24" s="10">
+        <v>2</v>
+      </c>
+      <c r="E24" s="10">
+        <v>4</v>
+      </c>
+      <c r="F24" s="10">
+        <v>38</v>
+      </c>
+      <c r="G24" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="H24" s="10"/>
       <c r="I24">
         <v>1.9</v>
       </c>
       <c r="J24" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="25" x14ac:dyDescent="0.45">
+      <c r="A25" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B25">
-        <v>14</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="B25" s="10">
+        <v>10</v>
+      </c>
+      <c r="C25" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="10">
+        <v>3</v>
+      </c>
+      <c r="E25" s="10">
         <v>4</v>
       </c>
-      <c r="E25">
-        <v>6</v>
-      </c>
-      <c r="F25">
-        <v>48</v>
-      </c>
-      <c r="G25">
-        <v>2</v>
-      </c>
-      <c r="H25" t="s">
-        <v>316</v>
+      <c r="F25" s="10">
+        <v>40</v>
+      </c>
+      <c r="G25" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>423</v>
       </c>
       <c r="I25">
         <v>1.9</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
+      <c r="A26" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B26">
-        <v>14</v>
-      </c>
-      <c r="C26" t="s">
-        <v>172</v>
-      </c>
-      <c r="D26">
-        <v>4</v>
-      </c>
-      <c r="E26">
-        <v>6</v>
-      </c>
-      <c r="F26">
-        <v>48</v>
-      </c>
-      <c r="G26">
+      <c r="B26" s="10">
+        <v>10</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D26" s="10">
         <v>2</v>
       </c>
+      <c r="E26" s="10">
+        <v>5</v>
+      </c>
+      <c r="F26" s="10">
+        <v>40</v>
+      </c>
+      <c r="G26" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="H26" s="10"/>
       <c r="I26">
         <v>2</v>
       </c>
       <c r="J26" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="25" x14ac:dyDescent="0.45">
+      <c r="A27" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B27">
-        <v>15</v>
-      </c>
-      <c r="C27" t="s">
-        <v>172</v>
-      </c>
-      <c r="D27">
-        <v>3</v>
-      </c>
-      <c r="E27">
-        <v>6</v>
-      </c>
-      <c r="F27">
-        <v>50</v>
-      </c>
-      <c r="G27">
-        <v>2.1</v>
-      </c>
-      <c r="H27" t="s">
-        <v>318</v>
+      <c r="B27" s="10">
+        <v>10</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="D27" s="10">
+        <v>2</v>
+      </c>
+      <c r="E27" s="10">
+        <v>4</v>
+      </c>
+      <c r="F27" s="10">
+        <v>40</v>
+      </c>
+      <c r="G27" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>424</v>
       </c>
       <c r="I27">
         <v>2.1</v>
       </c>
       <c r="J27" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="25" x14ac:dyDescent="0.45">
+      <c r="A28" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B28">
-        <v>15</v>
-      </c>
-      <c r="C28" t="s">
-        <v>172</v>
-      </c>
-      <c r="D28">
+      <c r="B28" s="10">
+        <v>11</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="D28" s="10">
+        <v>2</v>
+      </c>
+      <c r="E28" s="10">
         <v>4</v>
       </c>
-      <c r="E28">
-        <v>6</v>
-      </c>
-      <c r="F28">
-        <v>50</v>
-      </c>
-      <c r="G28">
-        <v>2.1</v>
+      <c r="F28" s="10">
+        <v>42</v>
+      </c>
+      <c r="G28" s="10">
+        <v>1.55</v>
+      </c>
+      <c r="H28" s="10" t="s">
+        <v>425</v>
       </c>
       <c r="I28">
         <v>2.2000000000000002</v>
       </c>
       <c r="J28" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
+      <c r="A29" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B29">
-        <v>15</v>
-      </c>
-      <c r="C29" t="s">
-        <v>175</v>
-      </c>
-      <c r="D29">
-        <v>1</v>
-      </c>
-      <c r="E29">
-        <v>6</v>
-      </c>
-      <c r="F29">
-        <v>50</v>
-      </c>
-      <c r="G29">
-        <v>2.1</v>
-      </c>
+      <c r="B29" s="10">
+        <v>11</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="D29" s="10">
+        <v>3</v>
+      </c>
+      <c r="E29" s="10">
+        <v>4</v>
+      </c>
+      <c r="F29" s="10">
+        <v>42</v>
+      </c>
+      <c r="G29" s="10">
+        <v>1.55</v>
+      </c>
+      <c r="H29" s="10"/>
       <c r="I29">
         <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A30" t="s">
+      <c r="A30" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B30">
-        <v>16</v>
-      </c>
-      <c r="C30" t="s">
-        <v>172</v>
-      </c>
-      <c r="D30">
+      <c r="B30" s="10">
+        <v>11</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="D30" s="10">
         <v>2</v>
       </c>
-      <c r="E30">
-        <v>6</v>
-      </c>
-      <c r="F30">
-        <v>52</v>
-      </c>
-      <c r="G30">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="H30" t="s">
-        <v>321</v>
-      </c>
+      <c r="E30" s="10">
+        <v>4</v>
+      </c>
+      <c r="F30" s="10">
+        <v>42</v>
+      </c>
+      <c r="G30" s="10">
+        <v>1.55</v>
+      </c>
+      <c r="H30" s="10"/>
       <c r="I30">
         <v>2.2999999999999998</v>
       </c>
       <c r="J30" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A31" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="25" x14ac:dyDescent="0.45">
+      <c r="A31" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B31">
-        <v>16</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="B31" s="10">
+        <v>12</v>
+      </c>
+      <c r="C31" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="10">
+        <v>3</v>
+      </c>
+      <c r="E31" s="10">
         <v>4</v>
       </c>
-      <c r="E31">
-        <v>6</v>
-      </c>
-      <c r="F31">
-        <v>52</v>
-      </c>
-      <c r="G31">
-        <v>2.2000000000000002</v>
+      <c r="F31" s="10">
+        <v>45</v>
+      </c>
+      <c r="G31" s="10">
+        <v>1.6</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>426</v>
       </c>
       <c r="I31">
         <v>2.4</v>
       </c>
       <c r="J31" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A32" t="s">
+      <c r="A32" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B32">
-        <v>16</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="B32" s="10">
+        <v>12</v>
+      </c>
+      <c r="C32" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="10">
         <v>2</v>
       </c>
-      <c r="E32">
-        <v>6</v>
-      </c>
-      <c r="F32">
-        <v>52</v>
-      </c>
-      <c r="G32">
-        <v>2.2000000000000002</v>
-      </c>
+      <c r="E32" s="10">
+        <v>5</v>
+      </c>
+      <c r="F32" s="10">
+        <v>45</v>
+      </c>
+      <c r="G32" s="10">
+        <v>1.6</v>
+      </c>
+      <c r="H32" s="10"/>
       <c r="I32">
         <v>2.4</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A33" t="s">
+    <row r="33" spans="1:10" ht="25" x14ac:dyDescent="0.45">
+      <c r="A33" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B33">
-        <v>17</v>
-      </c>
-      <c r="C33" t="s">
-        <v>172</v>
-      </c>
-      <c r="D33">
+      <c r="B33" s="10">
+        <v>12</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="D33" s="10">
+        <v>2</v>
+      </c>
+      <c r="E33" s="10">
         <v>4</v>
       </c>
-      <c r="E33">
-        <v>6</v>
-      </c>
-      <c r="F33">
-        <v>55</v>
-      </c>
-      <c r="G33">
-        <v>2.4</v>
-      </c>
-      <c r="H33" t="s">
-        <v>324</v>
+      <c r="F33" s="10">
+        <v>45</v>
+      </c>
+      <c r="G33" s="10">
+        <v>1.6</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>427</v>
       </c>
       <c r="I33">
         <v>2.4</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A34" t="s">
+      <c r="A34" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B34">
-        <v>17</v>
-      </c>
-      <c r="C34" t="s">
-        <v>175</v>
-      </c>
-      <c r="D34">
-        <v>3</v>
-      </c>
-      <c r="E34">
-        <v>6</v>
-      </c>
-      <c r="F34">
-        <v>55</v>
-      </c>
-      <c r="G34">
-        <v>2.4</v>
+      <c r="B34" s="10">
+        <v>13</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="D34" s="10">
+        <v>2</v>
+      </c>
+      <c r="E34" s="10">
+        <v>4</v>
+      </c>
+      <c r="F34" s="10">
+        <v>48</v>
+      </c>
+      <c r="G34" s="10">
+        <v>1.7</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>428</v>
       </c>
       <c r="I34">
         <v>2.4</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A35" t="s">
+      <c r="A35" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B35">
-        <v>18</v>
-      </c>
-      <c r="C35" t="s">
-        <v>172</v>
-      </c>
-      <c r="D35">
+      <c r="B35" s="10">
+        <v>13</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="D35" s="10">
+        <v>3</v>
+      </c>
+      <c r="E35" s="10">
         <v>4</v>
       </c>
-      <c r="E35">
-        <v>6</v>
-      </c>
-      <c r="F35">
-        <v>58</v>
-      </c>
-      <c r="G35">
-        <v>2.6</v>
-      </c>
-      <c r="H35" t="s">
-        <v>325</v>
-      </c>
+      <c r="F35" s="10">
+        <v>48</v>
+      </c>
+      <c r="G35" s="10">
+        <v>1.7</v>
+      </c>
+      <c r="H35" s="10"/>
       <c r="I35">
         <v>2.5</v>
       </c>
       <c r="J35" t="s">
-        <v>326</v>
+        <v>308</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A36" t="s">
+      <c r="A36" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B36">
-        <v>18</v>
-      </c>
-      <c r="C36" t="s">
-        <v>175</v>
-      </c>
-      <c r="D36">
+      <c r="B36" s="10">
+        <v>13</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="D36" s="10">
+        <v>2</v>
+      </c>
+      <c r="E36" s="10">
         <v>4</v>
       </c>
-      <c r="E36">
-        <v>6</v>
-      </c>
-      <c r="F36">
-        <v>58</v>
-      </c>
-      <c r="G36">
-        <v>2.6</v>
-      </c>
+      <c r="F36" s="10">
+        <v>48</v>
+      </c>
+      <c r="G36" s="10">
+        <v>1.7</v>
+      </c>
+      <c r="H36" s="10"/>
       <c r="I36">
         <v>2.6</v>
       </c>
       <c r="J36" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A37" t="s">
+      <c r="A37" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B37">
-        <v>19</v>
-      </c>
-      <c r="C37" t="s">
-        <v>172</v>
-      </c>
-      <c r="D37">
+      <c r="B37" s="10">
+        <v>13</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="D37" s="10">
         <v>2</v>
       </c>
-      <c r="E37">
-        <v>6</v>
-      </c>
-      <c r="F37">
-        <v>60</v>
-      </c>
-      <c r="G37">
-        <v>3</v>
-      </c>
-      <c r="H37" t="s">
-        <v>328</v>
-      </c>
+      <c r="E37" s="10">
+        <v>4</v>
+      </c>
+      <c r="F37" s="10">
+        <v>48</v>
+      </c>
+      <c r="G37" s="10">
+        <v>1.7</v>
+      </c>
+      <c r="H37" s="10"/>
       <c r="I37">
         <v>2.7</v>
       </c>
       <c r="J37" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A38" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="25" x14ac:dyDescent="0.45">
+      <c r="A38" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B38">
-        <v>19</v>
-      </c>
-      <c r="C38" t="s">
-        <v>175</v>
-      </c>
-      <c r="D38">
-        <v>6</v>
-      </c>
-      <c r="E38">
-        <v>6</v>
-      </c>
-      <c r="F38">
-        <v>60</v>
-      </c>
-      <c r="G38">
-        <v>3</v>
+      <c r="B38" s="10">
+        <v>14</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="D38" s="10">
+        <v>4</v>
+      </c>
+      <c r="E38" s="10">
+        <v>4</v>
+      </c>
+      <c r="F38" s="10">
+        <v>50</v>
+      </c>
+      <c r="G38" s="10">
+        <v>1.8</v>
+      </c>
+      <c r="H38" s="10" t="s">
+        <v>429</v>
       </c>
       <c r="I38">
         <v>2.7</v>
       </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A39" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="B39" s="10">
+        <v>14</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D39" s="10">
+        <v>3</v>
+      </c>
+      <c r="E39" s="10">
+        <v>5</v>
+      </c>
+      <c r="F39" s="10">
+        <v>50</v>
+      </c>
+      <c r="G39" s="10">
+        <v>1.8</v>
+      </c>
+      <c r="H39" s="10"/>
+    </row>
+    <row r="40" spans="1:10" ht="25" x14ac:dyDescent="0.45">
+      <c r="A40" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="B40" s="10">
+        <v>14</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="D40" s="10">
+        <v>1</v>
+      </c>
+      <c r="E40" s="10">
+        <v>8</v>
+      </c>
+      <c r="F40" s="10">
+        <v>50</v>
+      </c>
+      <c r="G40" s="10">
+        <v>1.8</v>
+      </c>
+      <c r="H40" s="10" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A41" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="B41" s="10">
+        <v>15</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D41" s="10">
+        <v>3</v>
+      </c>
+      <c r="E41" s="10">
+        <v>5</v>
+      </c>
+      <c r="F41" s="10">
+        <v>52</v>
+      </c>
+      <c r="G41" s="10">
+        <v>1.9</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A42" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="B42" s="10">
+        <v>15</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="D42" s="10">
+        <v>4</v>
+      </c>
+      <c r="E42" s="10">
+        <v>4</v>
+      </c>
+      <c r="F42" s="10">
+        <v>52</v>
+      </c>
+      <c r="G42" s="10">
+        <v>1.9</v>
+      </c>
+      <c r="H42" s="10"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A43" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="B43" s="10">
+        <v>15</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="D43" s="10">
+        <v>1</v>
+      </c>
+      <c r="E43" s="10">
+        <v>8</v>
+      </c>
+      <c r="F43" s="10">
+        <v>52</v>
+      </c>
+      <c r="G43" s="10">
+        <v>1.9</v>
+      </c>
+      <c r="H43" s="10"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A44" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="B44" s="10">
+        <v>15</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="D44" s="10">
+        <v>3</v>
+      </c>
+      <c r="E44" s="10">
+        <v>4</v>
+      </c>
+      <c r="F44" s="10">
+        <v>52</v>
+      </c>
+      <c r="G44" s="10">
+        <v>1.9</v>
+      </c>
+      <c r="H44" s="10"/>
+    </row>
+    <row r="45" spans="1:10" ht="25" x14ac:dyDescent="0.45">
+      <c r="A45" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="B45" s="10">
+        <v>16</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="D45" s="10">
+        <v>4</v>
+      </c>
+      <c r="E45" s="10">
+        <v>4</v>
+      </c>
+      <c r="F45" s="10">
+        <v>55</v>
+      </c>
+      <c r="G45" s="10">
+        <v>2</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A46" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="B46" s="10">
+        <v>16</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="D46" s="10">
+        <v>2</v>
+      </c>
+      <c r="E46" s="10">
+        <v>8</v>
+      </c>
+      <c r="F46" s="10">
+        <v>55</v>
+      </c>
+      <c r="G46" s="10">
+        <v>2</v>
+      </c>
+      <c r="H46" s="10"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A47" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="B47" s="10">
+        <v>16</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="D47" s="10">
+        <v>3</v>
+      </c>
+      <c r="E47" s="10">
+        <v>4</v>
+      </c>
+      <c r="F47" s="10">
+        <v>55</v>
+      </c>
+      <c r="G47" s="10">
+        <v>2</v>
+      </c>
+      <c r="H47" s="10"/>
+    </row>
+    <row r="48" spans="1:10" ht="25" x14ac:dyDescent="0.45">
+      <c r="A48" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="B48" s="10">
+        <v>16</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="D48" s="10">
+        <v>1</v>
+      </c>
+      <c r="E48" s="10">
+        <v>10</v>
+      </c>
+      <c r="F48" s="10">
+        <v>55</v>
+      </c>
+      <c r="G48" s="10">
+        <v>2</v>
+      </c>
+      <c r="H48" s="10" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="25" x14ac:dyDescent="0.45">
+      <c r="A49" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="B49" s="10">
+        <v>17</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D49" s="10">
+        <v>3</v>
+      </c>
+      <c r="E49" s="10">
+        <v>4</v>
+      </c>
+      <c r="F49" s="10">
+        <v>58</v>
+      </c>
+      <c r="G49" s="10">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A50" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="B50" s="10">
+        <v>17</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="D50" s="10">
+        <v>4</v>
+      </c>
+      <c r="E50" s="10">
+        <v>4</v>
+      </c>
+      <c r="F50" s="10">
+        <v>58</v>
+      </c>
+      <c r="G50" s="10">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H50" s="10"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A51" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="B51" s="10">
+        <v>17</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="D51" s="10">
+        <v>2</v>
+      </c>
+      <c r="E51" s="10">
+        <v>8</v>
+      </c>
+      <c r="F51" s="10">
+        <v>58</v>
+      </c>
+      <c r="G51" s="10">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H51" s="10"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A52" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="B52" s="10">
+        <v>17</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="D52" s="10">
+        <v>1</v>
+      </c>
+      <c r="E52" s="10">
+        <v>10</v>
+      </c>
+      <c r="F52" s="10">
+        <v>58</v>
+      </c>
+      <c r="G52" s="10">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H52" s="10"/>
+    </row>
+    <row r="53" spans="1:8" ht="25" x14ac:dyDescent="0.45">
+      <c r="A53" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="B53" s="10">
+        <v>18</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="D53" s="10">
+        <v>5</v>
+      </c>
+      <c r="E53" s="10">
+        <v>3</v>
+      </c>
+      <c r="F53" s="10">
+        <v>60</v>
+      </c>
+      <c r="G53" s="10">
+        <v>2.4</v>
+      </c>
+      <c r="H53" s="10" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A54" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="B54" s="10">
+        <v>18</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="D54" s="10">
+        <v>4</v>
+      </c>
+      <c r="E54" s="10">
+        <v>3</v>
+      </c>
+      <c r="F54" s="10">
+        <v>60</v>
+      </c>
+      <c r="G54" s="10">
+        <v>2.4</v>
+      </c>
+      <c r="H54" s="10"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A55" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="B55" s="10">
+        <v>18</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="D55" s="10">
+        <v>3</v>
+      </c>
+      <c r="E55" s="10">
+        <v>4</v>
+      </c>
+      <c r="F55" s="10">
+        <v>60</v>
+      </c>
+      <c r="G55" s="10">
+        <v>2.4</v>
+      </c>
+      <c r="H55" s="10"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A56" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="B56" s="10">
+        <v>18</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="D56" s="10">
+        <v>2</v>
+      </c>
+      <c r="E56" s="10">
+        <v>8</v>
+      </c>
+      <c r="F56" s="10">
+        <v>60</v>
+      </c>
+      <c r="G56" s="10">
+        <v>2.4</v>
+      </c>
+      <c r="H56" s="10"/>
+    </row>
+    <row r="57" spans="1:8" ht="25" x14ac:dyDescent="0.45">
+      <c r="A57" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="B57" s="10">
+        <v>19</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D57" s="10">
+        <v>4</v>
+      </c>
+      <c r="E57" s="10">
+        <v>4</v>
+      </c>
+      <c r="F57" s="10">
+        <v>65</v>
+      </c>
+      <c r="G57" s="10">
+        <v>2.6</v>
+      </c>
+      <c r="H57" s="10" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A58" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="B58" s="10">
+        <v>19</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="D58" s="10">
+        <v>2</v>
+      </c>
+      <c r="E58" s="10">
+        <v>8</v>
+      </c>
+      <c r="F58" s="10">
+        <v>65</v>
+      </c>
+      <c r="G58" s="10">
+        <v>2.6</v>
+      </c>
+      <c r="H58" s="10"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A59" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="B59" s="10">
+        <v>19</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="D59" s="10">
+        <v>3</v>
+      </c>
+      <c r="E59" s="10">
+        <v>4</v>
+      </c>
+      <c r="F59" s="10">
+        <v>65</v>
+      </c>
+      <c r="G59" s="10">
+        <v>2.6</v>
+      </c>
+      <c r="H59" s="10"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A60" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="B60" s="10">
+        <v>19</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="D60" s="10">
+        <v>2</v>
+      </c>
+      <c r="E60" s="10">
+        <v>8</v>
+      </c>
+      <c r="F60" s="10">
+        <v>65</v>
+      </c>
+      <c r="G60" s="10">
+        <v>2.6</v>
+      </c>
+      <c r="H60" s="10"/>
+    </row>
+    <row r="61" spans="1:8" ht="25" x14ac:dyDescent="0.45">
+      <c r="A61" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="B61" s="10">
+        <v>20</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="D61" s="10">
+        <v>5</v>
+      </c>
+      <c r="E61" s="10">
+        <v>3</v>
+      </c>
+      <c r="F61" s="10">
+        <v>70</v>
+      </c>
+      <c r="G61" s="10">
+        <v>3</v>
+      </c>
+      <c r="H61" s="10" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="25" x14ac:dyDescent="0.45">
+      <c r="A62" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="B62" s="9">
+        <v>21</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="D62" s="9">
+        <v>5</v>
+      </c>
+      <c r="E62" s="9">
+        <v>4</v>
+      </c>
+      <c r="F62" s="9">
+        <v>70</v>
+      </c>
+      <c r="G62" s="9">
+        <v>3</v>
+      </c>
+      <c r="H62" s="9" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A63" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="B63" s="9">
+        <v>21</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="D63" s="9">
+        <v>4</v>
+      </c>
+      <c r="E63" s="9">
+        <v>4</v>
+      </c>
+      <c r="F63" s="9">
+        <v>70</v>
+      </c>
+      <c r="G63" s="9">
+        <v>3</v>
+      </c>
+      <c r="H63" s="9" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A64" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="B64" s="9">
+        <v>21</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="D64" s="9">
+        <v>3</v>
+      </c>
+      <c r="E64" s="9">
+        <v>4</v>
+      </c>
+      <c r="F64" s="9">
+        <v>70</v>
+      </c>
+      <c r="G64" s="9">
+        <v>3</v>
+      </c>
+      <c r="H64" s="9"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A65" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="B65" s="9">
+        <v>21</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="D65" s="9">
+        <v>2</v>
+      </c>
+      <c r="E65" s="9">
+        <v>8</v>
+      </c>
+      <c r="F65" s="9">
+        <v>70</v>
+      </c>
+      <c r="G65" s="9">
+        <v>3</v>
+      </c>
+      <c r="H65" s="9"/>
+    </row>
+    <row r="66" spans="1:8" ht="37.5" x14ac:dyDescent="0.45">
+      <c r="A66" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="B66" s="9">
+        <v>22</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="D66" s="9">
+        <v>4</v>
+      </c>
+      <c r="E66" s="9">
+        <v>4</v>
+      </c>
+      <c r="F66" s="9">
+        <v>80</v>
+      </c>
+      <c r="G66" s="9">
+        <v>3.8</v>
+      </c>
+      <c r="H66" s="9" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="25" x14ac:dyDescent="0.45">
+      <c r="A67" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="B67" s="9">
+        <v>22</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="D67" s="9">
+        <v>5</v>
+      </c>
+      <c r="E67" s="9">
+        <v>3</v>
+      </c>
+      <c r="F67" s="9">
+        <v>80</v>
+      </c>
+      <c r="G67" s="9">
+        <v>3.8</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A68" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="B68" s="9">
+        <v>22</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="D68" s="9">
+        <v>2</v>
+      </c>
+      <c r="E68" s="9">
+        <v>6</v>
+      </c>
+      <c r="F68" s="9">
+        <v>80</v>
+      </c>
+      <c r="G68" s="9">
+        <v>3.8</v>
+      </c>
+      <c r="H68" s="9"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A69" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="B69" s="9">
+        <v>22</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="D69" s="9">
+        <v>4</v>
+      </c>
+      <c r="E69" s="9">
+        <v>4</v>
+      </c>
+      <c r="F69" s="9">
+        <v>80</v>
+      </c>
+      <c r="G69" s="9">
+        <v>3.8</v>
+      </c>
+      <c r="H69" s="9"/>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A70" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="B70" s="9">
+        <v>22</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="D70" s="9">
+        <v>3</v>
+      </c>
+      <c r="E70" s="9">
+        <v>6</v>
+      </c>
+      <c r="F70" s="9">
+        <v>80</v>
+      </c>
+      <c r="G70" s="9">
+        <v>3.8</v>
+      </c>
+      <c r="H70" s="9"/>
+    </row>
+    <row r="71" spans="1:8" ht="37.5" x14ac:dyDescent="0.45">
+      <c r="A71" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="B71" s="9">
+        <v>23</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="D71" s="9">
+        <v>5</v>
+      </c>
+      <c r="E71" s="9">
+        <v>3</v>
+      </c>
+      <c r="F71" s="9">
+        <v>90</v>
+      </c>
+      <c r="G71" s="9">
+        <v>5</v>
+      </c>
+      <c r="H71" s="9" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="25" x14ac:dyDescent="0.45">
+      <c r="A72" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="B72" s="9">
+        <v>23</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="D72" s="9">
+        <v>6</v>
+      </c>
+      <c r="E72" s="9">
+        <v>3</v>
+      </c>
+      <c r="F72" s="9">
+        <v>90</v>
+      </c>
+      <c r="G72" s="9">
+        <v>5</v>
+      </c>
+      <c r="H72" s="9" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A73" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="B73" s="9">
+        <v>23</v>
+      </c>
+      <c r="C73" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="D73" s="9">
+        <v>3</v>
+      </c>
+      <c r="E73" s="9">
+        <v>5</v>
+      </c>
+      <c r="F73" s="9">
+        <v>90</v>
+      </c>
+      <c r="G73" s="9">
+        <v>5</v>
+      </c>
+      <c r="H73" s="9"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A74" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="B74" s="9">
+        <v>23</v>
+      </c>
+      <c r="C74" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="D74" s="9">
+        <v>4</v>
+      </c>
+      <c r="E74" s="9">
+        <v>3</v>
+      </c>
+      <c r="F74" s="9">
+        <v>90</v>
+      </c>
+      <c r="G74" s="9">
+        <v>5</v>
+      </c>
+      <c r="H74" s="9"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A75" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="B75" s="9">
+        <v>23</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="D75" s="9">
+        <v>4</v>
+      </c>
+      <c r="E75" s="9">
+        <v>5</v>
+      </c>
+      <c r="F75" s="9">
+        <v>90</v>
+      </c>
+      <c r="G75" s="9">
+        <v>5</v>
+      </c>
+      <c r="H75" s="9"/>
+    </row>
+    <row r="76" spans="1:8" ht="25" x14ac:dyDescent="0.45">
+      <c r="A76" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="B76" s="9">
+        <v>24</v>
+      </c>
+      <c r="C76" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="D76" s="9">
+        <v>6</v>
+      </c>
+      <c r="E76" s="9">
+        <v>2</v>
+      </c>
+      <c r="F76" s="9">
+        <v>999</v>
+      </c>
+      <c r="G76" s="9">
+        <v>8</v>
+      </c>
+      <c r="H76" s="9" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="25" x14ac:dyDescent="0.45">
+      <c r="A77" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="B77" s="9">
+        <v>24</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="D77" s="9">
+        <v>8</v>
+      </c>
+      <c r="E77" s="9">
+        <v>2</v>
+      </c>
+      <c r="F77" s="9">
+        <v>999</v>
+      </c>
+      <c r="G77" s="9">
+        <v>8</v>
+      </c>
+      <c r="H77" s="9" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A78" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="B78" s="9">
+        <v>24</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="D78" s="9">
+        <v>5</v>
+      </c>
+      <c r="E78" s="9">
+        <v>3</v>
+      </c>
+      <c r="F78" s="9">
+        <v>999</v>
+      </c>
+      <c r="G78" s="9">
+        <v>8</v>
+      </c>
+      <c r="H78" s="9"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A79" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="B79" s="9">
+        <v>24</v>
+      </c>
+      <c r="C79" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="D79" s="9">
+        <v>6</v>
+      </c>
+      <c r="E79" s="9">
+        <v>2</v>
+      </c>
+      <c r="F79" s="9">
+        <v>999</v>
+      </c>
+      <c r="G79" s="9">
+        <v>8</v>
+      </c>
+      <c r="H79" s="9"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A80" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="B80" s="9">
+        <v>24</v>
+      </c>
+      <c r="C80" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="D80" s="9">
+        <v>5</v>
+      </c>
+      <c r="E80" s="9">
+        <v>3</v>
+      </c>
+      <c r="F80" s="9">
+        <v>999</v>
+      </c>
+      <c r="G80" s="9">
+        <v>8</v>
+      </c>
+      <c r="H80" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -7071,16 +8694,16 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>329</v>
+        <v>310</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>330</v>
+        <v>311</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>331</v>
+        <v>312</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>332</v>
+        <v>313</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>289</v>
@@ -7100,7 +8723,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>333</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
@@ -7159,7 +8782,7 @@
         <v>1.5</v>
       </c>
       <c r="E6" t="s">
-        <v>334</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
@@ -7204,7 +8827,7 @@
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>335</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
@@ -7251,46 +8874,46 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>329</v>
+        <v>310</v>
       </c>
       <c r="B14" t="s">
-        <v>336</v>
+        <v>317</v>
       </c>
       <c r="C14" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>330</v>
+        <v>311</v>
       </c>
       <c r="B15" t="s">
         <v>66</v>
       </c>
       <c r="C15" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>331</v>
+        <v>312</v>
       </c>
       <c r="B16" t="s">
         <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>339</v>
+        <v>320</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>332</v>
+        <v>313</v>
       </c>
       <c r="B17" t="s">
         <v>57</v>
       </c>
       <c r="C17" t="s">
-        <v>340</v>
+        <v>321</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.45">
@@ -7301,7 +8924,7 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>341</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>

--- a/Table/car_survivor_tables.xlsx
+++ b/Table/car_survivor_tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PBL\CarSurvival_Plan\Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2605DBFD-312F-4ADC-88E2-8157DF8A369D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E635F8BD-2002-4278-928F-17435F58EE0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TB_Currency" sheetId="1" r:id="rId1"/>
@@ -37,6 +37,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>System</author>
+    <author>김영제</author>
   </authors>
   <commentList>
     <comment ref="M1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
@@ -340,12 +341,181 @@
         </r>
       </text>
     </comment>
+    <comment ref="M5" authorId="1" shapeId="0" xr:uid="{F2013E51-5650-45DB-833B-BC5A194CFA74}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>김영제</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>체인</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>횟수</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>레벨당</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>횟수</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>증가</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>예</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: LV1: 1 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>→</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> LV2: 2</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="497">
   <si>
     <t>currency_id</t>
   </si>
@@ -1727,13 +1897,148 @@
   </si>
   <si>
     <t>MON_035</t>
+  </si>
+  <si>
+    <t>BOOK_004</t>
+  </si>
+  <si>
+    <t>BOOK_005</t>
+  </si>
+  <si>
+    <t>BOOK_006</t>
+  </si>
+  <si>
+    <t>LANG_BOOK_004_NAME</t>
+  </si>
+  <si>
+    <t>LANG_BOOK_005_NAME</t>
+  </si>
+  <si>
+    <t>LANG_BOOK_006_NAME</t>
+  </si>
+  <si>
+    <t>HP Regen</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EXP Boost</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage Shield</t>
+  </si>
+  <si>
+    <t>BOOK_007</t>
+  </si>
+  <si>
+    <t>LANG_BOOK_007_NAME</t>
+  </si>
+  <si>
+    <t>LANG_BOOK_004_DESC</t>
+  </si>
+  <si>
+    <t>LANG_BOOK_005_DESC</t>
+  </si>
+  <si>
+    <t>LANG_BOOK_006_DESC</t>
+  </si>
+  <si>
+    <t>LANG_BOOK_007_DESC</t>
+  </si>
+  <si>
+    <t>Flamethrower</t>
+  </si>
+  <si>
+    <t>ChainLightning</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EMPPulse</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>LaserCannon</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MissilePod</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>weapon_emppulse</t>
+  </si>
+  <si>
+    <t>weapon_flamethrower</t>
+  </si>
+  <si>
+    <t>weapon_lasercannon</t>
+  </si>
+  <si>
+    <t>weapon_missilepod</t>
+  </si>
+  <si>
+    <t>Magnet</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage Shield</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>WPN_004</t>
+  </si>
+  <si>
+    <t>WPN_005</t>
+  </si>
+  <si>
+    <t>WPN_006</t>
+  </si>
+  <si>
+    <t>WPN_007</t>
+  </si>
+  <si>
+    <t>WPN_008</t>
+  </si>
+  <si>
+    <t>LANG_WPN_004_NAME</t>
+  </si>
+  <si>
+    <t>LANG_WPN_004_DESC</t>
+  </si>
+  <si>
+    <t>LANG_WPN_005_NAME</t>
+  </si>
+  <si>
+    <t>LANG_WPN_005_DESC</t>
+  </si>
+  <si>
+    <t>LANG_WPN_006_NAME</t>
+  </si>
+  <si>
+    <t>LANG_WPN_006_DESC</t>
+  </si>
+  <si>
+    <t>LANG_WPN_007_NAME</t>
+  </si>
+  <si>
+    <t>LANG_WPN_007_DESC</t>
+  </si>
+  <si>
+    <t>LANG_WPN_008_NAME</t>
+  </si>
+  <si>
+    <t>LANG_WPN_008_DESC</t>
+  </si>
+  <si>
+    <t>weapon_chainlightning</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1773,6 +2078,48 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="8">
@@ -1846,7 +2193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1868,6 +2215,17 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2171,14 +2529,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="2" width="17" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2192,7 +2550,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -2206,7 +2564,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -2220,7 +2578,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -2231,7 +2589,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -2242,7 +2600,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>1</v>
       </c>
@@ -2253,7 +2611,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -2264,7 +2622,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -2284,7 +2642,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -2297,7 +2655,7 @@
     <col min="9" max="9" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>323</v>
       </c>
@@ -2326,7 +2684,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>329</v>
       </c>
@@ -2355,7 +2713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
@@ -2366,7 +2724,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
         <v>323</v>
       </c>
@@ -2377,7 +2735,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>324</v>
       </c>
@@ -2388,7 +2746,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
         <v>325</v>
       </c>
@@ -2399,7 +2757,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
         <v>163</v>
       </c>
@@ -2410,7 +2768,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
         <v>283</v>
       </c>
@@ -2421,7 +2779,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
         <v>326</v>
       </c>
@@ -2432,7 +2790,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
         <v>327</v>
       </c>
@@ -2443,7 +2801,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
         <v>328</v>
       </c>
@@ -2454,7 +2812,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -2474,9 +2832,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>341</v>
       </c>
@@ -2487,7 +2845,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>89</v>
       </c>
@@ -2498,7 +2856,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>96</v>
       </c>
@@ -2509,7 +2867,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>103</v>
       </c>
@@ -2520,7 +2878,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>130</v>
       </c>
@@ -2531,7 +2889,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>134</v>
       </c>
@@ -2542,7 +2900,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>139</v>
       </c>
@@ -2562,9 +2920,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>341</v>
       </c>
@@ -2575,7 +2933,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>89</v>
       </c>
@@ -2586,7 +2944,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>96</v>
       </c>
@@ -2597,7 +2955,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>103</v>
       </c>
@@ -2608,7 +2966,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>130</v>
       </c>
@@ -2619,7 +2977,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>134</v>
       </c>
@@ -2630,7 +2988,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>139</v>
       </c>
@@ -2650,9 +3008,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>364</v>
       </c>
@@ -2684,7 +3042,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>373</v>
       </c>
@@ -2716,7 +3074,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>379</v>
       </c>
@@ -2748,7 +3106,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>384</v>
       </c>
@@ -2790,7 +3148,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2800,9 +3158,9 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>372</v>
       </c>
@@ -2831,7 +3189,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>378</v>
       </c>
@@ -2860,7 +3218,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>378</v>
       </c>
@@ -2889,7 +3247,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>378</v>
       </c>
@@ -2918,7 +3276,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
         <v>378</v>
       </c>
@@ -2947,7 +3305,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>378</v>
       </c>
@@ -2976,7 +3334,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
         <v>383</v>
       </c>
@@ -3005,7 +3363,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
         <v>383</v>
       </c>
@@ -3034,7 +3392,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
         <v>383</v>
       </c>
@@ -3063,7 +3421,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
         <v>383</v>
       </c>
@@ -3092,7 +3450,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
         <v>388</v>
       </c>
@@ -3121,7 +3479,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
         <v>388</v>
       </c>
@@ -3150,7 +3508,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
         <v>388</v>
       </c>
@@ -3179,7 +3537,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
         <v>388</v>
       </c>
@@ -3217,7 +3575,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O21"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -3236,7 +3594,7 @@
     <col min="15" max="15" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
@@ -3283,7 +3641,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
         <v>36</v>
       </c>
@@ -3330,7 +3688,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
         <v>42</v>
       </c>
@@ -3377,7 +3735,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
         <v>47</v>
       </c>
@@ -3424,7 +3782,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:15">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -3435,7 +3793,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:15">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -3446,7 +3804,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:15">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -3457,7 +3815,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:15">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -3468,7 +3826,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:15">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -3479,7 +3837,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:15">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -3490,7 +3848,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:15">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -3501,7 +3859,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:15">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -3512,7 +3870,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:15">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -3523,7 +3881,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:15">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -3534,7 +3892,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:15">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -3545,7 +3903,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>31</v>
       </c>
@@ -3556,7 +3914,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>32</v>
       </c>
@@ -3567,7 +3925,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>33</v>
       </c>
@@ -3578,7 +3936,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -3589,7 +3947,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>35</v>
       </c>
@@ -3608,8 +3966,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Q23"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:Q41"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -3625,7 +3983,7 @@
     <col min="13" max="17" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>73</v>
       </c>
@@ -3678,7 +4036,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
         <v>89</v>
       </c>
@@ -3731,7 +4089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:17">
       <c r="A3" t="s">
         <v>96</v>
       </c>
@@ -3784,254 +4142,491 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
+    <row r="4" spans="1:17">
+      <c r="A4" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="14">
         <v>15</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="14">
         <v>0</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="14">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="14">
         <v>5</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="14">
         <v>8</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="14">
         <v>180</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="14">
         <v>6</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="14">
         <v>0.3</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="14">
         <v>0</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="14">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A6" s="2" t="s">
+    <row r="5" spans="1:17">
+      <c r="A5" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>486</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" s="15">
+        <v>30</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>487</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>471</v>
+      </c>
+      <c r="H5" s="11">
+        <v>4</v>
+      </c>
+      <c r="I5" s="11">
+        <v>0</v>
+      </c>
+      <c r="J5" s="11">
+        <v>5</v>
+      </c>
+      <c r="K5" s="11">
+        <v>7</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>496</v>
+      </c>
+      <c r="M5" s="13">
+        <v>1</v>
+      </c>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6" s="15" t="s">
+        <v>482</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" s="15">
+        <v>3</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>489</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>472</v>
+      </c>
+      <c r="H6" s="11">
+        <v>8</v>
+      </c>
+      <c r="I6" s="11">
+        <v>2</v>
+      </c>
+      <c r="J6" s="11">
+        <v>5</v>
+      </c>
+      <c r="K6" s="11">
+        <v>7</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>475</v>
+      </c>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
+      <c r="P6" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="15" t="s">
+        <v>483</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>490</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7" s="15">
+        <v>15</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>491</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>470</v>
+      </c>
+      <c r="H7" s="11">
+        <v>0</v>
+      </c>
+      <c r="I7" s="11">
+        <v>0</v>
+      </c>
+      <c r="J7" s="11">
+        <v>5</v>
+      </c>
+      <c r="K7" s="11">
+        <v>8</v>
+      </c>
+      <c r="L7" s="12" t="s">
+        <v>476</v>
+      </c>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8" s="15" t="s">
+        <v>484</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>492</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" s="15">
+        <v>30</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>493</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>473</v>
+      </c>
+      <c r="H8" s="11">
+        <v>3</v>
+      </c>
+      <c r="I8" s="11">
+        <v>1</v>
+      </c>
+      <c r="J8" s="11">
+        <v>5</v>
+      </c>
+      <c r="K8" s="11">
+        <v>6</v>
+      </c>
+      <c r="L8" s="12" t="s">
+        <v>477</v>
+      </c>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9" s="15" t="s">
+        <v>485</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>494</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="D9" s="15">
+        <v>20</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>495</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>474</v>
+      </c>
+      <c r="H9" s="11">
+        <v>5</v>
+      </c>
+      <c r="I9" s="11">
+        <v>0</v>
+      </c>
+      <c r="J9" s="11">
+        <v>5</v>
+      </c>
+      <c r="K9" s="11">
+        <v>7</v>
+      </c>
+      <c r="L9" s="12" t="s">
+        <v>478</v>
+      </c>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B24" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C24" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
         <v>73</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B25" t="s">
         <v>15</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C25" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
         <v>74</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B26" t="s">
         <v>17</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C26" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
         <v>75</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B27" t="s">
         <v>55</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C27" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
         <v>76</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B28" t="s">
         <v>57</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C28" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
         <v>77</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B29" t="s">
         <v>17</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C29" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
         <v>78</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B30" t="s">
         <v>55</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C30" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
         <v>79</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B31" t="s">
         <v>55</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C31" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
         <v>80</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B32" t="s">
         <v>57</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C32" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
         <v>81</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B33" t="s">
         <v>57</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C33" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
         <v>82</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B34" t="s">
         <v>66</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C34" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
         <v>83</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B35" t="s">
         <v>66</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C35" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
         <v>3</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B36" t="s">
         <v>17</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C36" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
         <v>84</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B37" t="s">
         <v>57</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C37" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
         <v>85</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B38" t="s">
         <v>57</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C38" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
         <v>86</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B39" t="s">
         <v>57</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C39" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
         <v>87</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B40" t="s">
         <v>57</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C40" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
         <v>88</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B41" t="s">
         <v>57</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C41" t="s">
         <v>124</v>
       </c>
     </row>
@@ -4044,8 +4639,8 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I15"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:I19"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="22.1640625" bestFit="1" customWidth="1"/>
@@ -4057,7 +4652,7 @@
     <col min="9" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>125</v>
       </c>
@@ -4086,7 +4681,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>130</v>
       </c>
@@ -4115,7 +4710,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>134</v>
       </c>
@@ -4144,7 +4739,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>139</v>
       </c>
@@ -4173,113 +4768,229 @@
         <v>143</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A6" s="2" t="s">
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>455</v>
+      </c>
+      <c r="B5" t="s">
+        <v>458</v>
+      </c>
+      <c r="C5" t="s">
+        <v>461</v>
+      </c>
+      <c r="D5">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>466</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>456</v>
+      </c>
+      <c r="B6" t="s">
+        <v>459</v>
+      </c>
+      <c r="C6" t="s">
+        <v>462</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>467</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>10</v>
+      </c>
+      <c r="I6" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>457</v>
+      </c>
+      <c r="B7" t="s">
+        <v>460</v>
+      </c>
+      <c r="C7" t="s">
+        <v>480</v>
+      </c>
+      <c r="D7">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
+        <v>468</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>10</v>
+      </c>
+      <c r="I7" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>464</v>
+      </c>
+      <c r="B8" t="s">
+        <v>465</v>
+      </c>
+      <c r="C8" t="s">
+        <v>479</v>
+      </c>
+      <c r="D8">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
+        <v>469</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>10</v>
+      </c>
+      <c r="I8" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
         <v>125</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B11" t="s">
         <v>15</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C11" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
         <v>126</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B12" t="s">
         <v>17</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C12" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
         <v>127</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B13" t="s">
         <v>55</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C13" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
         <v>128</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B14" t="s">
         <v>57</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C14" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
         <v>77</v>
-      </c>
-      <c r="B11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>82</v>
-      </c>
-      <c r="B12" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>129</v>
-      </c>
-      <c r="B13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>83</v>
-      </c>
-      <c r="B14" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>3</v>
       </c>
       <c r="B15" t="s">
         <v>17</v>
       </c>
       <c r="C15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>129</v>
+      </c>
+      <c r="B17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>83</v>
+      </c>
+      <c r="B18" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" t="s">
         <v>119</v>
       </c>
     </row>
@@ -4292,7 +5003,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -4303,7 +5014,7 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>149</v>
       </c>
@@ -4326,7 +5037,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
@@ -4337,7 +5048,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>149</v>
       </c>
@@ -4348,7 +5059,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>150</v>
       </c>
@@ -4359,7 +5070,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>151</v>
       </c>
@@ -4370,7 +5081,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>127</v>
       </c>
@@ -4381,7 +5092,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>152</v>
       </c>
@@ -4392,7 +5103,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>82</v>
       </c>
@@ -4403,7 +5114,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -4423,7 +5134,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:N37"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -4439,7 +5150,7 @@
     <col min="13" max="13" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>158</v>
       </c>
@@ -4483,7 +5194,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>168</v>
       </c>
@@ -4527,7 +5238,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>172</v>
       </c>
@@ -4571,7 +5282,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>175</v>
       </c>
@@ -4615,7 +5326,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>178</v>
       </c>
@@ -4659,7 +5370,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
         <v>403</v>
       </c>
@@ -4700,7 +5411,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
         <v>404</v>
       </c>
@@ -4741,7 +5452,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
         <v>405</v>
       </c>
@@ -4782,7 +5493,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
         <v>406</v>
       </c>
@@ -4823,7 +5534,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
         <v>407</v>
       </c>
@@ -4864,7 +5575,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
         <v>182</v>
       </c>
@@ -4908,7 +5619,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
         <v>408</v>
       </c>
@@ -4949,7 +5660,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
         <v>409</v>
       </c>
@@ -4990,7 +5701,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
         <v>204</v>
       </c>
@@ -5031,7 +5742,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
         <v>207</v>
       </c>
@@ -5072,7 +5783,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
         <v>210</v>
       </c>
@@ -5113,7 +5824,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
         <v>213</v>
       </c>
@@ -5154,7 +5865,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
         <v>216</v>
       </c>
@@ -5195,7 +5906,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
         <v>219</v>
       </c>
@@ -5236,7 +5947,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
         <v>222</v>
       </c>
@@ -5277,7 +5988,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:14">
       <c r="A21" t="s">
         <v>225</v>
       </c>
@@ -5318,7 +6029,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
         <v>228</v>
       </c>
@@ -5359,7 +6070,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:14">
       <c r="A23" t="s">
         <v>231</v>
       </c>
@@ -5400,7 +6111,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:14">
       <c r="A24" t="s">
         <v>234</v>
       </c>
@@ -5441,7 +6152,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:14">
       <c r="A25" t="s">
         <v>237</v>
       </c>
@@ -5482,7 +6193,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:14">
       <c r="A26" t="s">
         <v>240</v>
       </c>
@@ -5523,7 +6234,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:14">
       <c r="A27" t="s">
         <v>243</v>
       </c>
@@ -5564,7 +6275,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:14">
       <c r="A28" t="s">
         <v>246</v>
       </c>
@@ -5605,7 +6316,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:14">
       <c r="A29" t="s">
         <v>446</v>
       </c>
@@ -5649,7 +6360,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:14">
       <c r="A30" t="s">
         <v>447</v>
       </c>
@@ -5693,7 +6404,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:14">
       <c r="A31" t="s">
         <v>448</v>
       </c>
@@ -5737,7 +6448,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:14">
       <c r="A32" t="s">
         <v>449</v>
       </c>
@@ -5781,7 +6492,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:14">
       <c r="A33" t="s">
         <v>450</v>
       </c>
@@ -5822,7 +6533,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:14">
       <c r="A34" t="s">
         <v>451</v>
       </c>
@@ -5863,7 +6574,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:14">
       <c r="A35" t="s">
         <v>452</v>
       </c>
@@ -5904,7 +6615,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:14">
       <c r="A36" t="s">
         <v>453</v>
       </c>
@@ -5945,7 +6656,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:14">
       <c r="A37" t="s">
         <v>454</v>
       </c>
@@ -5996,7 +6707,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
@@ -6004,7 +6715,7 @@
     <col min="5" max="5" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>252</v>
       </c>
@@ -6021,7 +6732,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>256</v>
       </c>
@@ -6038,7 +6749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>257</v>
       </c>
@@ -6055,7 +6766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>258</v>
       </c>
@@ -6072,7 +6783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>259</v>
       </c>
@@ -6089,7 +6800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>260</v>
       </c>
@@ -6106,7 +6817,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>261</v>
       </c>
@@ -6123,7 +6834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>262</v>
       </c>
@@ -6140,7 +6851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>263</v>
       </c>
@@ -6157,7 +6868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>264</v>
       </c>
@@ -6174,7 +6885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>265</v>
       </c>
@@ -6191,7 +6902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>266</v>
       </c>
@@ -6208,7 +6919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>267</v>
       </c>
@@ -6225,7 +6936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>268</v>
       </c>
@@ -6242,7 +6953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
         <v>269</v>
       </c>
@@ -6259,7 +6970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>270</v>
       </c>
@@ -6276,7 +6987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>271</v>
       </c>
@@ -6293,7 +7004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>272</v>
       </c>
@@ -6310,7 +7021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>273</v>
       </c>
@@ -6327,7 +7038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>274</v>
       </c>
@@ -6344,7 +7055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>275</v>
       </c>
@@ -6361,7 +7072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
         <v>276</v>
       </c>
@@ -6378,7 +7089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>277</v>
       </c>
@@ -6395,7 +7106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
         <v>278</v>
       </c>
@@ -6412,7 +7123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
         <v>279</v>
       </c>
@@ -6429,7 +7140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
         <v>280</v>
       </c>
@@ -6446,7 +7157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
         <v>281</v>
       </c>
@@ -6463,7 +7174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:5">
       <c r="A28" t="s">
         <v>282</v>
       </c>
@@ -6490,7 +7201,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:J80"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
@@ -6503,7 +7214,7 @@
     <col min="9" max="9" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>283</v>
       </c>
@@ -6535,7 +7246,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="25" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" ht="25">
       <c r="A2" s="10" t="s">
         <v>290</v>
       </c>
@@ -6567,7 +7278,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="25" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" ht="25">
       <c r="A3" s="10" t="s">
         <v>290</v>
       </c>
@@ -6596,7 +7307,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10">
       <c r="A4" s="10" t="s">
         <v>290</v>
       </c>
@@ -6625,7 +7336,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="25" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" ht="25">
       <c r="A5" s="10" t="s">
         <v>290</v>
       </c>
@@ -6654,7 +7365,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10">
       <c r="A6" s="10" t="s">
         <v>290</v>
       </c>
@@ -6683,7 +7394,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10">
       <c r="A7" s="10" t="s">
         <v>290</v>
       </c>
@@ -6715,7 +7426,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10">
       <c r="A8" s="10" t="s">
         <v>290</v>
       </c>
@@ -6742,7 +7453,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10">
       <c r="A9" s="10" t="s">
         <v>290</v>
       </c>
@@ -6769,7 +7480,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="25" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" ht="25">
       <c r="A10" s="10" t="s">
         <v>290</v>
       </c>
@@ -6801,7 +7512,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="25" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" ht="25">
       <c r="A11" s="10" t="s">
         <v>290</v>
       </c>
@@ -6830,7 +7541,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10">
       <c r="A12" s="10" t="s">
         <v>290</v>
       </c>
@@ -6862,7 +7573,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:10">
       <c r="A13" s="10" t="s">
         <v>290</v>
       </c>
@@ -6892,7 +7603,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:10">
       <c r="A14" s="10" t="s">
         <v>290</v>
       </c>
@@ -6922,7 +7633,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="25" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:10" ht="25">
       <c r="A15" s="10" t="s">
         <v>290</v>
       </c>
@@ -6954,7 +7665,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="25" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:10" ht="25">
       <c r="A16" s="10" t="s">
         <v>290</v>
       </c>
@@ -6983,7 +7694,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:10">
       <c r="A17" s="10" t="s">
         <v>290</v>
       </c>
@@ -7013,7 +7724,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="25" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:10" ht="25">
       <c r="A18" s="10" t="s">
         <v>290</v>
       </c>
@@ -7045,7 +7756,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:10">
       <c r="A19" s="10" t="s">
         <v>290</v>
       </c>
@@ -7072,7 +7783,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:10">
       <c r="A20" s="10" t="s">
         <v>290</v>
       </c>
@@ -7099,7 +7810,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:10">
       <c r="A21" s="10" t="s">
         <v>290</v>
       </c>
@@ -7131,7 +7842,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:10">
       <c r="A22" s="10" t="s">
         <v>290</v>
       </c>
@@ -7161,7 +7872,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:10">
       <c r="A23" s="10" t="s">
         <v>290</v>
       </c>
@@ -7188,7 +7899,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:10">
       <c r="A24" s="10" t="s">
         <v>290</v>
       </c>
@@ -7218,7 +7929,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="25" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:10" ht="25">
       <c r="A25" s="10" t="s">
         <v>290</v>
       </c>
@@ -7247,7 +7958,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:10">
       <c r="A26" s="10" t="s">
         <v>290</v>
       </c>
@@ -7277,7 +7988,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="25" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:10" ht="25">
       <c r="A27" s="10" t="s">
         <v>290</v>
       </c>
@@ -7309,7 +8020,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="25" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:10" ht="25">
       <c r="A28" s="10" t="s">
         <v>290</v>
       </c>
@@ -7341,7 +8052,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:10">
       <c r="A29" s="10" t="s">
         <v>290</v>
       </c>
@@ -7368,7 +8079,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:10">
       <c r="A30" s="10" t="s">
         <v>290</v>
       </c>
@@ -7398,7 +8109,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="25" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:10" ht="25">
       <c r="A31" s="10" t="s">
         <v>290</v>
       </c>
@@ -7430,7 +8141,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:10">
       <c r="A32" s="10" t="s">
         <v>290</v>
       </c>
@@ -7457,7 +8168,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="25" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:10" ht="25">
       <c r="A33" s="10" t="s">
         <v>290</v>
       </c>
@@ -7486,7 +8197,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:10">
       <c r="A34" s="10" t="s">
         <v>290</v>
       </c>
@@ -7515,7 +8226,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:10">
       <c r="A35" s="10" t="s">
         <v>290</v>
       </c>
@@ -7545,7 +8256,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:10">
       <c r="A36" s="10" t="s">
         <v>290</v>
       </c>
@@ -7575,7 +8286,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:10">
       <c r="A37" s="10" t="s">
         <v>290</v>
       </c>
@@ -7605,7 +8316,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="25" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:10" ht="25">
       <c r="A38" s="10" t="s">
         <v>290</v>
       </c>
@@ -7634,7 +8345,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:10">
       <c r="A39" s="10" t="s">
         <v>290</v>
       </c>
@@ -7658,7 +8369,7 @@
       </c>
       <c r="H39" s="10"/>
     </row>
-    <row r="40" spans="1:10" ht="25" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:10" ht="25">
       <c r="A40" s="10" t="s">
         <v>290</v>
       </c>
@@ -7684,7 +8395,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:10">
       <c r="A41" s="10" t="s">
         <v>290</v>
       </c>
@@ -7710,7 +8421,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:10">
       <c r="A42" s="10" t="s">
         <v>290</v>
       </c>
@@ -7734,7 +8445,7 @@
       </c>
       <c r="H42" s="10"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:10">
       <c r="A43" s="10" t="s">
         <v>290</v>
       </c>
@@ -7758,7 +8469,7 @@
       </c>
       <c r="H43" s="10"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:10">
       <c r="A44" s="10" t="s">
         <v>290</v>
       </c>
@@ -7782,7 +8493,7 @@
       </c>
       <c r="H44" s="10"/>
     </row>
-    <row r="45" spans="1:10" ht="25" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:10" ht="25">
       <c r="A45" s="10" t="s">
         <v>290</v>
       </c>
@@ -7808,7 +8519,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:10">
       <c r="A46" s="10" t="s">
         <v>290</v>
       </c>
@@ -7832,7 +8543,7 @@
       </c>
       <c r="H46" s="10"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:10">
       <c r="A47" s="10" t="s">
         <v>290</v>
       </c>
@@ -7856,7 +8567,7 @@
       </c>
       <c r="H47" s="10"/>
     </row>
-    <row r="48" spans="1:10" ht="25" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:10" ht="25">
       <c r="A48" s="10" t="s">
         <v>290</v>
       </c>
@@ -7882,7 +8593,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="25" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:8" ht="25">
       <c r="A49" s="10" t="s">
         <v>290</v>
       </c>
@@ -7908,7 +8619,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:8">
       <c r="A50" s="10" t="s">
         <v>290</v>
       </c>
@@ -7932,7 +8643,7 @@
       </c>
       <c r="H50" s="10"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:8">
       <c r="A51" s="10" t="s">
         <v>290</v>
       </c>
@@ -7956,7 +8667,7 @@
       </c>
       <c r="H51" s="10"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:8">
       <c r="A52" s="10" t="s">
         <v>290</v>
       </c>
@@ -7980,7 +8691,7 @@
       </c>
       <c r="H52" s="10"/>
     </row>
-    <row r="53" spans="1:8" ht="25" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:8" ht="25">
       <c r="A53" s="10" t="s">
         <v>290</v>
       </c>
@@ -8006,7 +8717,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:8">
       <c r="A54" s="10" t="s">
         <v>290</v>
       </c>
@@ -8030,7 +8741,7 @@
       </c>
       <c r="H54" s="10"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:8">
       <c r="A55" s="10" t="s">
         <v>290</v>
       </c>
@@ -8054,7 +8765,7 @@
       </c>
       <c r="H55" s="10"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:8">
       <c r="A56" s="10" t="s">
         <v>290</v>
       </c>
@@ -8078,7 +8789,7 @@
       </c>
       <c r="H56" s="10"/>
     </row>
-    <row r="57" spans="1:8" ht="25" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:8" ht="25">
       <c r="A57" s="10" t="s">
         <v>290</v>
       </c>
@@ -8104,7 +8815,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:8">
       <c r="A58" s="10" t="s">
         <v>290</v>
       </c>
@@ -8128,7 +8839,7 @@
       </c>
       <c r="H58" s="10"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:8">
       <c r="A59" s="10" t="s">
         <v>290</v>
       </c>
@@ -8152,7 +8863,7 @@
       </c>
       <c r="H59" s="10"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:8">
       <c r="A60" s="10" t="s">
         <v>290</v>
       </c>
@@ -8176,7 +8887,7 @@
       </c>
       <c r="H60" s="10"/>
     </row>
-    <row r="61" spans="1:8" ht="25" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:8" ht="25">
       <c r="A61" s="10" t="s">
         <v>290</v>
       </c>
@@ -8202,7 +8913,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="25" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:8" ht="25">
       <c r="A62" s="9" t="s">
         <v>290</v>
       </c>
@@ -8228,7 +8939,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:8">
       <c r="A63" s="9" t="s">
         <v>290</v>
       </c>
@@ -8254,7 +8965,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:8">
       <c r="A64" s="9" t="s">
         <v>290</v>
       </c>
@@ -8278,7 +8989,7 @@
       </c>
       <c r="H64" s="9"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:8">
       <c r="A65" s="9" t="s">
         <v>290</v>
       </c>
@@ -8302,7 +9013,7 @@
       </c>
       <c r="H65" s="9"/>
     </row>
-    <row r="66" spans="1:8" ht="37.5" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:8" ht="37.5">
       <c r="A66" s="9" t="s">
         <v>290</v>
       </c>
@@ -8328,7 +9039,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="25" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:8" ht="25">
       <c r="A67" s="9" t="s">
         <v>290</v>
       </c>
@@ -8354,7 +9065,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:8">
       <c r="A68" s="9" t="s">
         <v>290</v>
       </c>
@@ -8378,7 +9089,7 @@
       </c>
       <c r="H68" s="9"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:8">
       <c r="A69" s="9" t="s">
         <v>290</v>
       </c>
@@ -8402,7 +9113,7 @@
       </c>
       <c r="H69" s="9"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:8">
       <c r="A70" s="9" t="s">
         <v>290</v>
       </c>
@@ -8426,7 +9137,7 @@
       </c>
       <c r="H70" s="9"/>
     </row>
-    <row r="71" spans="1:8" ht="37.5" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:8" ht="37.5">
       <c r="A71" s="9" t="s">
         <v>290</v>
       </c>
@@ -8452,7 +9163,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="25" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:8" ht="25">
       <c r="A72" s="9" t="s">
         <v>290</v>
       </c>
@@ -8478,7 +9189,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:8">
       <c r="A73" s="9" t="s">
         <v>290</v>
       </c>
@@ -8502,7 +9213,7 @@
       </c>
       <c r="H73" s="9"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:8">
       <c r="A74" s="9" t="s">
         <v>290</v>
       </c>
@@ -8526,7 +9237,7 @@
       </c>
       <c r="H74" s="9"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:8">
       <c r="A75" s="9" t="s">
         <v>290</v>
       </c>
@@ -8550,7 +9261,7 @@
       </c>
       <c r="H75" s="9"/>
     </row>
-    <row r="76" spans="1:8" ht="25" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:8" ht="25">
       <c r="A76" s="9" t="s">
         <v>290</v>
       </c>
@@ -8576,7 +9287,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="25" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:8" ht="25">
       <c r="A77" s="9" t="s">
         <v>290</v>
       </c>
@@ -8602,7 +9313,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:8">
       <c r="A78" s="9" t="s">
         <v>290</v>
       </c>
@@ -8626,7 +9337,7 @@
       </c>
       <c r="H78" s="9"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:8">
       <c r="A79" s="9" t="s">
         <v>290</v>
       </c>
@@ -8650,7 +9361,7 @@
       </c>
       <c r="H79" s="9"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:8">
       <c r="A80" s="9" t="s">
         <v>290</v>
       </c>
@@ -8683,7 +9394,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:E18"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -8692,7 +9403,7 @@
     <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>310</v>
       </c>
@@ -8709,7 +9420,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
@@ -8726,7 +9437,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>2</v>
       </c>
@@ -8740,7 +9451,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>3</v>
       </c>
@@ -8754,7 +9465,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>4</v>
       </c>
@@ -8768,7 +9479,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>5</v>
       </c>
@@ -8785,7 +9496,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>6</v>
       </c>
@@ -8799,7 +9510,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>7</v>
       </c>
@@ -8813,7 +9524,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>8</v>
       </c>
@@ -8830,7 +9541,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>9</v>
       </c>
@@ -8844,7 +9555,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>10</v>
       </c>
@@ -8861,7 +9572,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
@@ -8872,7 +9583,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>310</v>
       </c>
@@ -8883,7 +9594,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
         <v>311</v>
       </c>
@@ -8894,7 +9605,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>312</v>
       </c>
@@ -8905,7 +9616,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>313</v>
       </c>
@@ -8916,7 +9627,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>289</v>
       </c>

--- a/Table/car_survivor_tables.xlsx
+++ b/Table/car_survivor_tables.xlsx
@@ -367,6 +367,22 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>System</author>
+  </authors>
+  <commentList>
+    <comment ref="P1" authorId="0" shapeId="0">
+      <text>
+        <t>화염방사기 오프셋 거리
+차량 앞 불꽃 위치 (최소 3)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>System</author>
     <author>TableDesigner</author>
   </authors>
   <commentList>
@@ -375,7 +391,10 @@
         <t>etc_value1
 MachineGun: (미사용)
 OilSlick: 감속 비율 (%)
-SawBlade: 회전 속도 (도/초)</t>
+SawBlade: 회전 속도 (도/초)
+Flamethrower: 화상 데미지
+ChainLightning: 기본 타격 인원
+EMPPulse: 타격 간격 (초)</t>
       </text>
     </comment>
     <comment ref="N1" authorId="0" shapeId="0">
@@ -383,7 +402,10 @@
         <t>etc_value2
 MachineGun: (미사용)
 OilSlick: 감속 지속 시간 (초)
-SawBlade: 궤도 반경</t>
+SawBlade: 궤도 반경
+Flamethrower: 기본 반경
+ChainLightning: 레벨당 추가 인원
+EMPPulse: 기본 반경</t>
       </text>
     </comment>
     <comment ref="O1" authorId="0" shapeId="0">
@@ -391,7 +413,10 @@
         <t>etc_value3
 MachineGun: (미사용)
 OilSlick: 기본 반경
-SawBlade: 타격 간격 (초)</t>
+SawBlade: 타격 간격 (초)
+Flamethrower: 레벨당 반경 증가
+ChainLightning: 체인 범위
+EMPPulse: 레벨당 반경 증가</t>
       </text>
     </comment>
     <comment ref="P1" authorId="0" shapeId="0">
@@ -399,7 +424,8 @@
         <t>etc_value4 ★레벨당 증가량★
 MachineGun: 레벨당 데미지 증가
 OilSlick: 레벨당 범위 증가
-SawBlade: (미사용, 개수=레벨)</t>
+SawBlade: (미사용, 개수=레벨)
+Flamethrower: 화상 지속시간 (초)</t>
       </text>
     </comment>
     <comment ref="Q1" authorId="0" shapeId="0">
@@ -523,29 +549,32 @@
         <t>쿨타임 (초)</t>
       </text>
     </comment>
-    <comment ref="M5" authorId="1" shapeId="0">
+    <comment ref="M5" authorId="0" shapeId="0">
       <text>
-        <t>기본 타격 인원수</t>
+        <t>etc_value1: 기본 타격 인원
+기본 3</t>
       </text>
     </comment>
-    <comment ref="N5" authorId="1" shapeId="0">
+    <comment ref="N5" authorId="0" shapeId="0">
       <text>
-        <t>레벨당 추가 인원 (+1)</t>
+        <t>etc_value2: 레벨당 추가 인원
+기본 1</t>
       </text>
     </comment>
-    <comment ref="O5" authorId="1" shapeId="0">
+    <comment ref="O5" authorId="0" shapeId="0">
       <text>
-        <t>(미사용)</t>
+        <t>etc_value3: 체인 범위
+기본 5</t>
       </text>
     </comment>
-    <comment ref="P5" authorId="1" shapeId="0">
+    <comment ref="P5" authorId="0" shapeId="0">
       <text>
-        <t>(미사용)</t>
+        <t>etc_value4: (미사용)</t>
       </text>
     </comment>
-    <comment ref="Q5" authorId="1" shapeId="0">
+    <comment ref="Q5" authorId="0" shapeId="0">
       <text>
-        <t>(미사용)</t>
+        <t>etc_value5: (미사용)</t>
       </text>
     </comment>
     <comment ref="R5" authorId="1" shapeId="0">
@@ -568,29 +597,32 @@
         <t>스턴 지속시간 (초)</t>
       </text>
     </comment>
-    <comment ref="M6" authorId="1" shapeId="0">
+    <comment ref="M6" authorId="0" shapeId="0">
       <text>
-        <t>기본 스턴 지속시간 (초)</t>
+        <t>etc_value1: 타격 간격 (초)
+기본 0.5</t>
       </text>
     </comment>
-    <comment ref="N6" authorId="1" shapeId="0">
+    <comment ref="N6" authorId="0" shapeId="0">
       <text>
-        <t>기본 반경</t>
+        <t>etc_value2: 기본 반경
+기본 3</t>
       </text>
     </comment>
-    <comment ref="O6" authorId="1" shapeId="0">
+    <comment ref="O6" authorId="0" shapeId="0">
       <text>
-        <t>레벨당 반경 증가량</t>
+        <t>etc_value3: 레벨당 반경 증가
+기본 0.5</t>
       </text>
     </comment>
-    <comment ref="P6" authorId="1" shapeId="0">
+    <comment ref="P6" authorId="0" shapeId="0">
       <text>
-        <t>(미사용)</t>
+        <t>etc_value4: (미사용)</t>
       </text>
     </comment>
-    <comment ref="Q6" authorId="1" shapeId="0">
+    <comment ref="Q6" authorId="0" shapeId="0">
       <text>
-        <t>(미사용)</t>
+        <t>etc_value5: (미사용)</t>
       </text>
     </comment>
     <comment ref="R6" authorId="1" shapeId="0">
@@ -613,29 +645,33 @@
         <t>화염 지속시간 (초)</t>
       </text>
     </comment>
-    <comment ref="M7" authorId="1" shapeId="0">
+    <comment ref="M7" authorId="0" shapeId="0">
       <text>
-        <t>기본 화염 지속시간 (초)</t>
+        <t>etc_value1: 화상 데미지
+기본 8</t>
       </text>
     </comment>
-    <comment ref="N7" authorId="1" shapeId="0">
+    <comment ref="N7" authorId="0" shapeId="0">
       <text>
-        <t>기본 화염 반경</t>
+        <t>etc_value2: 기본 반경
+기본 2</t>
       </text>
     </comment>
-    <comment ref="O7" authorId="1" shapeId="0">
+    <comment ref="O7" authorId="0" shapeId="0">
       <text>
-        <t>레벨당 반경 증가량</t>
+        <t>etc_value3: 레벨당 반경 증가
+기본 0.3</t>
       </text>
     </comment>
-    <comment ref="P7" authorId="1" shapeId="0">
+    <comment ref="P7" authorId="0" shapeId="0">
       <text>
-        <t>(미사용)</t>
+        <t>etc_value4: 화상 지속시간 (초)
+기본 3</t>
       </text>
     </comment>
-    <comment ref="Q7" authorId="1" shapeId="0">
+    <comment ref="Q7" authorId="0" shapeId="0">
       <text>
-        <t>(미사용)</t>
+        <t>etc_value5: (미사용)</t>
       </text>
     </comment>
     <comment ref="R7" authorId="1" shapeId="0">
@@ -2783,7 +2819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2879,6 +2915,11 @@
           <t>sprite_key</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>flame_offset</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2940,6 +2981,9 @@
           <t>spr_car_super</t>
         </is>
       </c>
+      <c r="P2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3001,6 +3045,9 @@
           <t>spr_car_suv</t>
         </is>
       </c>
+      <c r="P3" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3062,6 +3109,9 @@
           <t>spr_car_motorcycle</t>
         </is>
       </c>
+      <c r="P4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -3337,6 +3387,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -3871,7 +3922,7 @@
         <v>0.3</v>
       </c>
       <c r="P7" s="23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q7" s="23" t="n">
         <v>0</v>
@@ -5168,7 +5219,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>HP Regen-removebg</t>
+          <t>ico_hpregen</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5258,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>EXP Boost-removebg</t>
+          <t>ico_expboost</t>
         </is>
       </c>
     </row>
@@ -5246,7 +5297,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Damage Shield-removebg</t>
+          <t>ico_damageshield</t>
         </is>
       </c>
     </row>
@@ -5285,10 +5336,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Magnet-removebg</t>
-        </is>
-      </c>
-    </row>
+          <t>ico_magnet</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
@@ -5770,7 +5822,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="E2" t="n">
         <v>2.5</v>
@@ -5822,7 +5874,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="E3" t="n">
         <v>4</v>
@@ -5874,7 +5926,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>120</v>
+        <v>1200</v>
       </c>
       <c r="E4" t="n">
         <v>1.5</v>
@@ -5926,7 +5978,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>40</v>
+        <v>400</v>
       </c>
       <c r="E5" t="n">
         <v>5</v>
@@ -5978,7 +6030,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>300</v>
+        <v>3000</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -6025,7 +6077,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="E7" t="n">
         <v>2.5</v>
@@ -6072,7 +6124,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -6119,7 +6171,7 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="E9" t="n">
         <v>1.5</v>
@@ -6166,7 +6218,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -6213,7 +6265,7 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>2000</v>
+        <v>20000</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -6265,7 +6317,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="E12" t="n">
         <v>0.5</v>
@@ -6312,7 +6364,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="E13" t="n">
         <v>1.5</v>
@@ -6359,7 +6411,7 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="E14" t="n">
         <v>1.5</v>
@@ -6406,7 +6458,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="E15" t="n">
         <v>1.5</v>
@@ -6453,7 +6505,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="E16" t="n">
         <v>1.5</v>
@@ -6500,7 +6552,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="E17" t="n">
         <v>1.5</v>
@@ -6547,7 +6599,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="E18" t="n">
         <v>1.5</v>
@@ -6594,7 +6646,7 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="E19" t="n">
         <v>1.5</v>
@@ -6641,7 +6693,7 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="E20" t="n">
         <v>1.5</v>
@@ -6688,7 +6740,7 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="E21" t="n">
         <v>1.5</v>
@@ -6735,7 +6787,7 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="E22" t="n">
         <v>1.5</v>
@@ -6782,7 +6834,7 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="E23" t="n">
         <v>1.5</v>
@@ -6829,7 +6881,7 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="E24" t="n">
         <v>1.5</v>
@@ -6876,7 +6928,7 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="E25" t="n">
         <v>1.5</v>
@@ -6923,7 +6975,7 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="E26" t="n">
         <v>1.5</v>
@@ -6970,7 +7022,7 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="E27" t="n">
         <v>1.5</v>
@@ -7017,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="E28" t="n">
         <v>1.5</v>
@@ -7064,7 +7116,7 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="E29" t="n">
         <v>2.5</v>
@@ -7116,7 +7168,7 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="E30" t="n">
         <v>4</v>
@@ -7168,7 +7220,7 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>120</v>
+        <v>1200</v>
       </c>
       <c r="E31" t="n">
         <v>1.5</v>
@@ -7220,7 +7272,7 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>40</v>
+        <v>400</v>
       </c>
       <c r="E32" t="n">
         <v>5</v>
@@ -7272,7 +7324,7 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>300</v>
+        <v>3000</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
@@ -7319,7 +7371,7 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="E34" t="n">
         <v>2.5</v>
@@ -7366,7 +7418,7 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
@@ -7413,7 +7465,7 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="E36" t="n">
         <v>1.5</v>
@@ -7460,7 +7512,7 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
@@ -8200,13 +8252,13 @@
         </is>
       </c>
       <c r="D2" s="10" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E2" s="10" t="n">
         <v>5</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="G2" s="10" t="n">
         <v>1</v>
@@ -8240,13 +8292,13 @@
         </is>
       </c>
       <c r="D3" s="10" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E3" s="10" t="n">
         <v>5</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="G3" s="10" t="n">
         <v>1.05</v>
@@ -8275,13 +8327,13 @@
         </is>
       </c>
       <c r="D4" s="10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E4" s="10" t="n">
         <v>5</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="G4" s="10" t="n">
         <v>1.05</v>
@@ -8310,13 +8362,13 @@
         </is>
       </c>
       <c r="D5" s="10" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E5" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>22</v>
+        <v>110</v>
       </c>
       <c r="G5" s="10" t="n">
         <v>1.1</v>
@@ -8345,13 +8397,13 @@
         </is>
       </c>
       <c r="D6" s="10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E6" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>22</v>
+        <v>110</v>
       </c>
       <c r="G6" s="10" t="n">
         <v>1.1</v>
@@ -8380,13 +8432,13 @@
         </is>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E7" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>1.15</v>
@@ -8420,13 +8472,13 @@
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E8" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="G8" s="10" t="n">
         <v>1.15</v>
@@ -8451,13 +8503,13 @@
         </is>
       </c>
       <c r="D9" s="10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E9" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="G9" s="10" t="n">
         <v>1.15</v>
@@ -8482,13 +8534,13 @@
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E10" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>28</v>
+        <v>140</v>
       </c>
       <c r="G10" s="10" t="n">
         <v>1.2</v>
@@ -8522,13 +8574,13 @@
         </is>
       </c>
       <c r="D11" s="10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E11" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>28</v>
+        <v>140</v>
       </c>
       <c r="G11" s="10" t="n">
         <v>1.2</v>
@@ -8557,13 +8609,13 @@
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E12" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="G12" s="10" t="n">
         <v>1.25</v>
@@ -8597,13 +8649,13 @@
         </is>
       </c>
       <c r="D13" s="10" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E13" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="G13" s="10" t="n">
         <v>1.25</v>
@@ -8633,13 +8685,13 @@
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E14" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="G14" s="10" t="n">
         <v>1.25</v>
@@ -8669,13 +8721,13 @@
         </is>
       </c>
       <c r="D15" s="10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E15" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>32</v>
+        <v>160</v>
       </c>
       <c r="G15" s="10" t="n">
         <v>1.3</v>
@@ -8709,13 +8761,13 @@
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>32</v>
+        <v>160</v>
       </c>
       <c r="G16" s="10" t="n">
         <v>1.3</v>
@@ -8744,13 +8796,13 @@
         </is>
       </c>
       <c r="D17" s="10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E17" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>32</v>
+        <v>160</v>
       </c>
       <c r="G17" s="10" t="n">
         <v>1.3</v>
@@ -8780,13 +8832,13 @@
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E18" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>35</v>
+        <v>175</v>
       </c>
       <c r="G18" s="10" t="n">
         <v>1.35</v>
@@ -8820,13 +8872,13 @@
         </is>
       </c>
       <c r="D19" s="10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>5</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>35</v>
+        <v>175</v>
       </c>
       <c r="G19" s="10" t="n">
         <v>1.35</v>
@@ -8851,13 +8903,13 @@
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E20" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>35</v>
+        <v>175</v>
       </c>
       <c r="G20" s="10" t="n">
         <v>1.35</v>
@@ -8882,13 +8934,13 @@
         </is>
       </c>
       <c r="D21" s="10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E21" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>38</v>
+        <v>190</v>
       </c>
       <c r="G21" s="10" t="n">
         <v>1.4</v>
@@ -8922,13 +8974,13 @@
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E22" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>38</v>
+        <v>190</v>
       </c>
       <c r="G22" s="10" t="n">
         <v>1.4</v>
@@ -8958,13 +9010,13 @@
         </is>
       </c>
       <c r="D23" s="10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E23" s="10" t="n">
         <v>5</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>38</v>
+        <v>190</v>
       </c>
       <c r="G23" s="10" t="n">
         <v>1.4</v>
@@ -8989,13 +9041,13 @@
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E24" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>38</v>
+        <v>190</v>
       </c>
       <c r="G24" s="10" t="n">
         <v>1.4</v>
@@ -9025,13 +9077,13 @@
         </is>
       </c>
       <c r="D25" s="10" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E25" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="G25" s="10" t="n">
         <v>1.5</v>
@@ -9060,13 +9112,13 @@
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E26" s="10" t="n">
         <v>5</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="G26" s="10" t="n">
         <v>1.5</v>
@@ -9096,13 +9148,13 @@
         </is>
       </c>
       <c r="D27" s="10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E27" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="G27" s="10" t="n">
         <v>1.5</v>
@@ -9136,13 +9188,13 @@
         </is>
       </c>
       <c r="D28" s="10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E28" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>42</v>
+        <v>210</v>
       </c>
       <c r="G28" s="10" t="n">
         <v>1.55</v>
@@ -9176,13 +9228,13 @@
         </is>
       </c>
       <c r="D29" s="10" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E29" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>42</v>
+        <v>210</v>
       </c>
       <c r="G29" s="10" t="n">
         <v>1.55</v>
@@ -9207,13 +9259,13 @@
         </is>
       </c>
       <c r="D30" s="10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>42</v>
+        <v>210</v>
       </c>
       <c r="G30" s="10" t="n">
         <v>1.55</v>
@@ -9243,13 +9295,13 @@
         </is>
       </c>
       <c r="D31" s="10" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E31" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>45</v>
+        <v>225</v>
       </c>
       <c r="G31" s="10" t="n">
         <v>1.6</v>
@@ -9283,13 +9335,13 @@
         </is>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E32" s="10" t="n">
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>45</v>
+        <v>225</v>
       </c>
       <c r="G32" s="10" t="n">
         <v>1.6</v>
@@ -9314,13 +9366,13 @@
         </is>
       </c>
       <c r="D33" s="10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E33" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>45</v>
+        <v>225</v>
       </c>
       <c r="G33" s="10" t="n">
         <v>1.6</v>
@@ -9349,13 +9401,13 @@
         </is>
       </c>
       <c r="D34" s="10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E34" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>48</v>
+        <v>240</v>
       </c>
       <c r="G34" s="10" t="n">
         <v>1.7</v>
@@ -9384,13 +9436,13 @@
         </is>
       </c>
       <c r="D35" s="10" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E35" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>48</v>
+        <v>240</v>
       </c>
       <c r="G35" s="10" t="n">
         <v>1.7</v>
@@ -9420,13 +9472,13 @@
         </is>
       </c>
       <c r="D36" s="10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E36" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>48</v>
+        <v>240</v>
       </c>
       <c r="G36" s="10" t="n">
         <v>1.7</v>
@@ -9456,13 +9508,13 @@
         </is>
       </c>
       <c r="D37" s="10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E37" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>48</v>
+        <v>240</v>
       </c>
       <c r="G37" s="10" t="n">
         <v>1.7</v>
@@ -9492,13 +9544,13 @@
         </is>
       </c>
       <c r="D38" s="10" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E38" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="G38" s="10" t="n">
         <v>1.8</v>
@@ -9527,13 +9579,13 @@
         </is>
       </c>
       <c r="D39" s="10" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E39" s="10" t="n">
         <v>5</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="G39" s="10" t="n">
         <v>1.8</v>
@@ -9555,13 +9607,13 @@
         </is>
       </c>
       <c r="D40" s="10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E40" s="10" t="n">
         <v>8</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="G40" s="10" t="n">
         <v>1.8</v>
@@ -9587,13 +9639,13 @@
         </is>
       </c>
       <c r="D41" s="10" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E41" s="10" t="n">
         <v>5</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>52</v>
+        <v>260</v>
       </c>
       <c r="G41" s="10" t="n">
         <v>1.9</v>
@@ -9619,13 +9671,13 @@
         </is>
       </c>
       <c r="D42" s="10" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E42" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>52</v>
+        <v>260</v>
       </c>
       <c r="G42" s="10" t="n">
         <v>1.9</v>
@@ -9647,13 +9699,13 @@
         </is>
       </c>
       <c r="D43" s="10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E43" s="10" t="n">
         <v>8</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>52</v>
+        <v>260</v>
       </c>
       <c r="G43" s="10" t="n">
         <v>1.9</v>
@@ -9675,13 +9727,13 @@
         </is>
       </c>
       <c r="D44" s="10" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E44" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>52</v>
+        <v>260</v>
       </c>
       <c r="G44" s="10" t="n">
         <v>1.9</v>
@@ -9703,13 +9755,13 @@
         </is>
       </c>
       <c r="D45" s="10" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E45" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>55</v>
+        <v>275</v>
       </c>
       <c r="G45" s="10" t="n">
         <v>2</v>
@@ -9735,13 +9787,13 @@
         </is>
       </c>
       <c r="D46" s="10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E46" s="10" t="n">
         <v>8</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>55</v>
+        <v>275</v>
       </c>
       <c r="G46" s="10" t="n">
         <v>2</v>
@@ -9763,13 +9815,13 @@
         </is>
       </c>
       <c r="D47" s="10" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E47" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>55</v>
+        <v>275</v>
       </c>
       <c r="G47" s="10" t="n">
         <v>2</v>
@@ -9791,13 +9843,13 @@
         </is>
       </c>
       <c r="D48" s="10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E48" s="10" t="n">
         <v>10</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>55</v>
+        <v>275</v>
       </c>
       <c r="G48" s="10" t="n">
         <v>2</v>
@@ -9823,13 +9875,13 @@
         </is>
       </c>
       <c r="D49" s="10" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E49" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>58</v>
+        <v>290</v>
       </c>
       <c r="G49" s="10" t="n">
         <v>2.2</v>
@@ -9855,13 +9907,13 @@
         </is>
       </c>
       <c r="D50" s="10" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E50" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>58</v>
+        <v>290</v>
       </c>
       <c r="G50" s="10" t="n">
         <v>2.2</v>
@@ -9883,13 +9935,13 @@
         </is>
       </c>
       <c r="D51" s="10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E51" s="10" t="n">
         <v>8</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>58</v>
+        <v>290</v>
       </c>
       <c r="G51" s="10" t="n">
         <v>2.2</v>
@@ -9911,13 +9963,13 @@
         </is>
       </c>
       <c r="D52" s="10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E52" s="10" t="n">
         <v>10</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>58</v>
+        <v>290</v>
       </c>
       <c r="G52" s="10" t="n">
         <v>2.2</v>
@@ -9939,13 +9991,13 @@
         </is>
       </c>
       <c r="D53" s="10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E53" s="10" t="n">
         <v>3</v>
       </c>
       <c r="F53" s="10" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="G53" s="10" t="n">
         <v>2.4</v>
@@ -9971,13 +10023,13 @@
         </is>
       </c>
       <c r="D54" s="10" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E54" s="10" t="n">
         <v>3</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="G54" s="10" t="n">
         <v>2.4</v>
@@ -9999,13 +10051,13 @@
         </is>
       </c>
       <c r="D55" s="10" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E55" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F55" s="10" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="G55" s="10" t="n">
         <v>2.4</v>
@@ -10027,13 +10079,13 @@
         </is>
       </c>
       <c r="D56" s="10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E56" s="10" t="n">
         <v>8</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="G56" s="10" t="n">
         <v>2.4</v>
@@ -10055,13 +10107,13 @@
         </is>
       </c>
       <c r="D57" s="10" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E57" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F57" s="10" t="n">
-        <v>65</v>
+        <v>325</v>
       </c>
       <c r="G57" s="10" t="n">
         <v>2.6</v>
@@ -10087,13 +10139,13 @@
         </is>
       </c>
       <c r="D58" s="10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E58" s="10" t="n">
         <v>8</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>65</v>
+        <v>325</v>
       </c>
       <c r="G58" s="10" t="n">
         <v>2.6</v>
@@ -10115,13 +10167,13 @@
         </is>
       </c>
       <c r="D59" s="10" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E59" s="10" t="n">
         <v>4</v>
       </c>
       <c r="F59" s="10" t="n">
-        <v>65</v>
+        <v>325</v>
       </c>
       <c r="G59" s="10" t="n">
         <v>2.6</v>
@@ -10143,13 +10195,13 @@
         </is>
       </c>
       <c r="D60" s="10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E60" s="10" t="n">
         <v>8</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>65</v>
+        <v>325</v>
       </c>
       <c r="G60" s="10" t="n">
         <v>2.6</v>
@@ -10171,13 +10223,13 @@
         </is>
       </c>
       <c r="D61" s="10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E61" s="10" t="n">
         <v>3</v>
       </c>
       <c r="F61" s="10" t="n">
-        <v>70</v>
+        <v>350</v>
       </c>
       <c r="G61" s="10" t="n">
         <v>3</v>
@@ -10203,13 +10255,13 @@
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E62" s="9" t="n">
         <v>4</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>70</v>
+        <v>350</v>
       </c>
       <c r="G62" s="9" t="n">
         <v>3</v>
@@ -10235,13 +10287,13 @@
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E63" s="9" t="n">
         <v>4</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>70</v>
+        <v>350</v>
       </c>
       <c r="G63" s="9" t="n">
         <v>3</v>
@@ -10267,13 +10319,13 @@
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E64" s="9" t="n">
         <v>4</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>70</v>
+        <v>350</v>
       </c>
       <c r="G64" s="9" t="n">
         <v>3</v>
@@ -10295,13 +10347,13 @@
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E65" s="9" t="n">
         <v>8</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>70</v>
+        <v>350</v>
       </c>
       <c r="G65" s="9" t="n">
         <v>3</v>
@@ -10323,13 +10375,13 @@
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E66" s="9" t="n">
         <v>4</v>
       </c>
       <c r="F66" s="9" t="n">
-        <v>80</v>
+        <v>400</v>
       </c>
       <c r="G66" s="9" t="n">
         <v>3.8</v>
@@ -10355,13 +10407,13 @@
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E67" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>80</v>
+        <v>400</v>
       </c>
       <c r="G67" s="9" t="n">
         <v>3.8</v>
@@ -10387,13 +10439,13 @@
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E68" s="9" t="n">
         <v>6</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>80</v>
+        <v>400</v>
       </c>
       <c r="G68" s="9" t="n">
         <v>3.8</v>
@@ -10415,13 +10467,13 @@
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E69" s="9" t="n">
         <v>4</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>80</v>
+        <v>400</v>
       </c>
       <c r="G69" s="9" t="n">
         <v>3.8</v>
@@ -10443,13 +10495,13 @@
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E70" s="9" t="n">
         <v>6</v>
       </c>
       <c r="F70" s="9" t="n">
-        <v>80</v>
+        <v>400</v>
       </c>
       <c r="G70" s="9" t="n">
         <v>3.8</v>
@@ -10471,13 +10523,13 @@
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E71" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>90</v>
+        <v>450</v>
       </c>
       <c r="G71" s="9" t="n">
         <v>5</v>
@@ -10503,13 +10555,13 @@
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="E72" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>90</v>
+        <v>450</v>
       </c>
       <c r="G72" s="9" t="n">
         <v>5</v>
@@ -10535,13 +10587,13 @@
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E73" s="9" t="n">
         <v>5</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>90</v>
+        <v>450</v>
       </c>
       <c r="G73" s="9" t="n">
         <v>5</v>
@@ -10563,13 +10615,13 @@
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E74" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F74" s="9" t="n">
-        <v>90</v>
+        <v>450</v>
       </c>
       <c r="G74" s="9" t="n">
         <v>5</v>
@@ -10591,13 +10643,13 @@
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E75" s="9" t="n">
         <v>5</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>90</v>
+        <v>450</v>
       </c>
       <c r="G75" s="9" t="n">
         <v>5</v>
@@ -10619,13 +10671,13 @@
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="E76" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>999</v>
+        <v>4995</v>
       </c>
       <c r="G76" s="9" t="n">
         <v>8</v>
@@ -10651,13 +10703,13 @@
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="E77" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>999</v>
+        <v>4995</v>
       </c>
       <c r="G77" s="9" t="n">
         <v>8</v>
@@ -10683,13 +10735,13 @@
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E78" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F78" s="9" t="n">
-        <v>999</v>
+        <v>4995</v>
       </c>
       <c r="G78" s="9" t="n">
         <v>8</v>
@@ -10711,13 +10763,13 @@
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="E79" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>999</v>
+        <v>4995</v>
       </c>
       <c r="G79" s="9" t="n">
         <v>8</v>
@@ -10739,13 +10791,13 @@
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E80" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F80" s="9" t="n">
-        <v>999</v>
+        <v>4995</v>
       </c>
       <c r="G80" s="9" t="n">
         <v>8</v>
